--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-08</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-02</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-01</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-31</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-30</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-29</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-08-27</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
         <v>101</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -549,7 +549,7 @@
         <v>100</v>
       </c>
       <c r="N2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -843,7 +843,7 @@
         <v>181</v>
       </c>
       <c r="H8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I8" t="n">
         <v>180</v>
@@ -861,7 +861,7 @@
         <v>180</v>
       </c>
       <c r="N8" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -965,7 +965,7 @@
         <v>73</v>
       </c>
       <c r="N10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1274,7 +1274,7 @@
         <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N16" t="n">
         <v>36</v>
@@ -1329,7 +1329,7 @@
         <v>64</v>
       </c>
       <c r="N17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -1794,7 +1794,7 @@
         <v>91</v>
       </c>
       <c r="M26" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N26" t="n">
         <v>90</v>
@@ -1898,7 +1898,7 @@
         <v>123</v>
       </c>
       <c r="M28" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N28" t="n">
         <v>122</v>
@@ -2455,7 +2455,7 @@
         <v>180</v>
       </c>
       <c r="H39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I39" t="n">
         <v>179</v>
@@ -2473,7 +2473,7 @@
         <v>179</v>
       </c>
       <c r="N39" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
@@ -3388,7 +3388,7 @@
         <v>147</v>
       </c>
       <c r="G57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>516</v>
+      </c>
+      <c r="F58" t="n">
         <v>512</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>511</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>510</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>501</v>
-      </c>
-      <c r="I58" t="n">
-        <v>498</v>
       </c>
       <c r="J58" t="n">
         <v>498</v>
       </c>
       <c r="K58" t="n">
+        <v>498</v>
+      </c>
+      <c r="L58" t="n">
         <v>495</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>494</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>492</v>
-      </c>
-      <c r="N58" t="n">
-        <v>491</v>
       </c>
     </row>
     <row r="59">
@@ -3905,7 +3905,7 @@
         <v>103</v>
       </c>
       <c r="F67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G67" t="n">
         <v>102</v>
@@ -3926,7 +3926,7 @@
         <v>102</v>
       </c>
       <c r="M67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N67" t="n">
         <v>101</v>
@@ -4489,7 +4489,7 @@
         <v>289</v>
       </c>
       <c r="J78" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K78" t="n">
         <v>288</v>
@@ -4688,7 +4688,7 @@
         <v>62</v>
       </c>
       <c r="G82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H82" t="n">
         <v>61</v>
@@ -4810,7 +4810,7 @@
         <v>56</v>
       </c>
       <c r="M84" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N84" t="n">
         <v>55</v>
@@ -5122,7 +5122,7 @@
         <v>210</v>
       </c>
       <c r="M90" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N90" t="n">
         <v>209</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-09</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-02</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-01</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-31</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-30</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-08-29</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         <v>101</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K2" t="n">
         <v>100</v>
@@ -846,7 +846,7 @@
         <v>181</v>
       </c>
       <c r="I8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J8" t="n">
         <v>180</v>
@@ -1277,7 +1277,7 @@
         <v>37</v>
       </c>
       <c r="N16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -1797,7 +1797,7 @@
         <v>91</v>
       </c>
       <c r="N26" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -1901,7 +1901,7 @@
         <v>123</v>
       </c>
       <c r="N28" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29">
@@ -2458,7 +2458,7 @@
         <v>180</v>
       </c>
       <c r="I39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J39" t="n">
         <v>179</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F55" t="n">
         <v>96</v>
@@ -3391,7 +3391,7 @@
         <v>147</v>
       </c>
       <c r="H57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>518</v>
+      </c>
+      <c r="F58" t="n">
         <v>516</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>512</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>511</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>510</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>501</v>
-      </c>
-      <c r="J58" t="n">
-        <v>498</v>
       </c>
       <c r="K58" t="n">
         <v>498</v>
       </c>
       <c r="L58" t="n">
+        <v>498</v>
+      </c>
+      <c r="M58" t="n">
         <v>495</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>494</v>
-      </c>
-      <c r="N58" t="n">
-        <v>492</v>
       </c>
     </row>
     <row r="59">
@@ -3908,7 +3908,7 @@
         <v>103</v>
       </c>
       <c r="G67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H67" t="n">
         <v>102</v>
@@ -3929,7 +3929,7 @@
         <v>102</v>
       </c>
       <c r="N67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68">
@@ -4492,7 +4492,7 @@
         <v>289</v>
       </c>
       <c r="K78" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L78" t="n">
         <v>288</v>
@@ -4691,7 +4691,7 @@
         <v>62</v>
       </c>
       <c r="H82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I82" t="n">
         <v>61</v>
@@ -4813,7 +4813,7 @@
         <v>56</v>
       </c>
       <c r="N84" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85">
@@ -5125,7 +5125,7 @@
         <v>210</v>
       </c>
       <c r="N90" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91">

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-10</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-02</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-01</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-08-31</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-08-30</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         <v>101</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F8" t="n">
         <v>181</v>
@@ -849,7 +849,7 @@
         <v>181</v>
       </c>
       <c r="J8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K8" t="n">
         <v>180</v>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F9" t="n">
         <v>129</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>73</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>68</v>
@@ -2461,7 +2461,7 @@
         <v>180</v>
       </c>
       <c r="J39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K39" t="n">
         <v>179</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F54" t="n">
         <v>31</v>
@@ -3281,7 +3281,7 @@
         <v>97</v>
       </c>
       <c r="F55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G55" t="n">
         <v>96</v>
@@ -3394,7 +3394,7 @@
         <v>147</v>
       </c>
       <c r="I57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>519</v>
+      </c>
+      <c r="F58" t="n">
         <v>518</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>516</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>512</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>511</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>510</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>501</v>
-      </c>
-      <c r="K58" t="n">
-        <v>498</v>
       </c>
       <c r="L58" t="n">
         <v>498</v>
       </c>
       <c r="M58" t="n">
+        <v>498</v>
+      </c>
+      <c r="N58" t="n">
         <v>495</v>
-      </c>
-      <c r="N58" t="n">
-        <v>494</v>
       </c>
     </row>
     <row r="59">
@@ -3911,7 +3911,7 @@
         <v>103</v>
       </c>
       <c r="H67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I67" t="n">
         <v>102</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F73" t="n">
         <v>77</v>
@@ -4495,7 +4495,7 @@
         <v>289</v>
       </c>
       <c r="L78" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M78" t="n">
         <v>288</v>
@@ -4694,7 +4694,7 @@
         <v>62</v>
       </c>
       <c r="I82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J82" t="n">
         <v>61</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-11</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-02</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-01</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-08-31</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
         <v>101</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -837,7 +837,7 @@
         <v>182</v>
       </c>
       <c r="F8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G8" t="n">
         <v>181</v>
@@ -852,7 +852,7 @@
         <v>181</v>
       </c>
       <c r="K8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L8" t="n">
         <v>180</v>
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="E9" t="n">
+        <v>131</v>
+      </c>
+      <c r="F9" t="n">
         <v>130</v>
-      </c>
-      <c r="F9" t="n">
-        <v>129</v>
       </c>
       <c r="G9" t="n">
         <v>129</v>
@@ -941,7 +941,7 @@
         <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" t="n">
         <v>73</v>
@@ -1045,7 +1045,7 @@
         <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>68</v>
@@ -2464,7 +2464,7 @@
         <v>180</v>
       </c>
       <c r="K39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L39" t="n">
         <v>179</v>
@@ -3229,7 +3229,7 @@
         <v>33</v>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G54" t="n">
         <v>31</v>
@@ -3284,7 +3284,7 @@
         <v>97</v>
       </c>
       <c r="G55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H55" t="n">
         <v>96</v>
@@ -3397,7 +3397,7 @@
         <v>147</v>
       </c>
       <c r="J57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>523</v>
+      </c>
+      <c r="F58" t="n">
         <v>519</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>518</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>516</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>512</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>511</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>510</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>501</v>
-      </c>
-      <c r="L58" t="n">
-        <v>498</v>
       </c>
       <c r="M58" t="n">
         <v>498</v>
       </c>
       <c r="N58" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="59">
@@ -3914,7 +3914,7 @@
         <v>103</v>
       </c>
       <c r="I67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J67" t="n">
         <v>102</v>
@@ -4217,7 +4217,7 @@
         <v>78</v>
       </c>
       <c r="F73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G73" t="n">
         <v>77</v>
@@ -4498,7 +4498,7 @@
         <v>289</v>
       </c>
       <c r="M78" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N78" t="n">
         <v>288</v>
@@ -4697,7 +4697,7 @@
         <v>62</v>
       </c>
       <c r="J82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K82" t="n">
         <v>61</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-12</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-02</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-01</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         <v>101</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -840,7 +840,7 @@
         <v>182</v>
       </c>
       <c r="G8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
         <v>181</v>
@@ -855,7 +855,7 @@
         <v>181</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M8" t="n">
         <v>180</v>
@@ -889,10 +889,10 @@
         <v>131</v>
       </c>
       <c r="F9" t="n">
+        <v>131</v>
+      </c>
+      <c r="G9" t="n">
         <v>130</v>
-      </c>
-      <c r="G9" t="n">
-        <v>129</v>
       </c>
       <c r="H9" t="n">
         <v>129</v>
@@ -944,7 +944,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" t="n">
         <v>73</v>
@@ -1048,7 +1048,7 @@
         <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" t="n">
         <v>68</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F39" t="n">
         <v>180</v>
@@ -2467,7 +2467,7 @@
         <v>180</v>
       </c>
       <c r="L39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M39" t="n">
         <v>179</v>
@@ -3232,7 +3232,7 @@
         <v>33</v>
       </c>
       <c r="G54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H54" t="n">
         <v>31</v>
@@ -3287,7 +3287,7 @@
         <v>97</v>
       </c>
       <c r="H55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I55" t="n">
         <v>96</v>
@@ -3400,7 +3400,7 @@
         <v>147</v>
       </c>
       <c r="K57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L57" t="n">
         <v>146</v>
@@ -3434,31 +3434,31 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>525</v>
+      </c>
+      <c r="F58" t="n">
         <v>523</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>519</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>518</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>516</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>512</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>511</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>510</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>501</v>
-      </c>
-      <c r="M58" t="n">
-        <v>498</v>
       </c>
       <c r="N58" t="n">
         <v>498</v>
@@ -3917,7 +3917,7 @@
         <v>103</v>
       </c>
       <c r="J67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K67" t="n">
         <v>102</v>
@@ -4220,7 +4220,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H73" t="n">
         <v>77</v>
@@ -4501,7 +4501,7 @@
         <v>289</v>
       </c>
       <c r="N78" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="79">
@@ -4700,7 +4700,7 @@
         <v>62</v>
       </c>
       <c r="K82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L82" t="n">
         <v>61</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-13</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-03</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-02</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>101</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -843,7 +843,7 @@
         <v>182</v>
       </c>
       <c r="H8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I8" t="n">
         <v>181</v>
@@ -858,7 +858,7 @@
         <v>181</v>
       </c>
       <c r="M8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N8" t="n">
         <v>180</v>
@@ -892,10 +892,10 @@
         <v>131</v>
       </c>
       <c r="G9" t="n">
+        <v>131</v>
+      </c>
+      <c r="H9" t="n">
         <v>130</v>
-      </c>
-      <c r="H9" t="n">
-        <v>129</v>
       </c>
       <c r="I9" t="n">
         <v>129</v>
@@ -947,7 +947,7 @@
         <v>74</v>
       </c>
       <c r="H10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I10" t="n">
         <v>73</v>
@@ -1051,7 +1051,7 @@
         <v>69</v>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" t="n">
         <v>68</v>
@@ -2449,7 +2449,7 @@
         <v>181</v>
       </c>
       <c r="F39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G39" t="n">
         <v>180</v>
@@ -2470,7 +2470,7 @@
         <v>180</v>
       </c>
       <c r="M39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N39" t="n">
         <v>179</v>
@@ -3235,7 +3235,7 @@
         <v>33</v>
       </c>
       <c r="H54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I54" t="n">
         <v>31</v>
@@ -3290,7 +3290,7 @@
         <v>97</v>
       </c>
       <c r="I55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J55" t="n">
         <v>96</v>
@@ -3403,7 +3403,7 @@
         <v>147</v>
       </c>
       <c r="L57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>530</v>
+      </c>
+      <c r="F58" t="n">
         <v>525</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>523</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>519</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>518</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>516</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>512</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>511</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>510</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>501</v>
-      </c>
-      <c r="N58" t="n">
-        <v>498</v>
       </c>
     </row>
     <row r="59">
@@ -3920,7 +3920,7 @@
         <v>103</v>
       </c>
       <c r="K67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L67" t="n">
         <v>102</v>
@@ -4223,7 +4223,7 @@
         <v>78</v>
       </c>
       <c r="H73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I73" t="n">
         <v>77</v>
@@ -4703,7 +4703,7 @@
         <v>62</v>
       </c>
       <c r="L82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M82" t="n">
         <v>61</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-14</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-05</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-03</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
         <v>182</v>
       </c>
       <c r="I8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J8" t="n">
         <v>181</v>
@@ -861,7 +861,7 @@
         <v>181</v>
       </c>
       <c r="N8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
@@ -895,10 +895,10 @@
         <v>131</v>
       </c>
       <c r="H9" t="n">
+        <v>131</v>
+      </c>
+      <c r="I9" t="n">
         <v>130</v>
-      </c>
-      <c r="I9" t="n">
-        <v>129</v>
       </c>
       <c r="J9" t="n">
         <v>129</v>
@@ -950,7 +950,7 @@
         <v>74</v>
       </c>
       <c r="I10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" t="n">
         <v>73</v>
@@ -1054,7 +1054,7 @@
         <v>69</v>
       </c>
       <c r="I12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J12" t="n">
         <v>68</v>
@@ -2452,7 +2452,7 @@
         <v>181</v>
       </c>
       <c r="G39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H39" t="n">
         <v>180</v>
@@ -2473,7 +2473,7 @@
         <v>180</v>
       </c>
       <c r="N39" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
@@ -3238,7 +3238,7 @@
         <v>33</v>
       </c>
       <c r="I54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J54" t="n">
         <v>31</v>
@@ -3293,7 +3293,7 @@
         <v>97</v>
       </c>
       <c r="J55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K55" t="n">
         <v>96</v>
@@ -3406,7 +3406,7 @@
         <v>147</v>
       </c>
       <c r="M57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N57" t="n">
         <v>146</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>531</v>
+      </c>
+      <c r="F58" t="n">
         <v>530</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>525</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>523</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>519</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>518</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>516</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>512</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>511</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>510</v>
-      </c>
-      <c r="N58" t="n">
-        <v>501</v>
       </c>
     </row>
     <row r="59">
@@ -3923,7 +3923,7 @@
         <v>103</v>
       </c>
       <c r="L67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M67" t="n">
         <v>102</v>
@@ -4226,7 +4226,7 @@
         <v>78</v>
       </c>
       <c r="I73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J73" t="n">
         <v>77</v>
@@ -4706,7 +4706,7 @@
         <v>62</v>
       </c>
       <c r="M82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N82" t="n">
         <v>61</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-15</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-06</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-05</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
         <v>182</v>
       </c>
       <c r="J8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K8" t="n">
         <v>181</v>
@@ -898,10 +898,10 @@
         <v>131</v>
       </c>
       <c r="I9" t="n">
+        <v>131</v>
+      </c>
+      <c r="J9" t="n">
         <v>130</v>
-      </c>
-      <c r="J9" t="n">
-        <v>129</v>
       </c>
       <c r="K9" t="n">
         <v>129</v>
@@ -953,7 +953,7 @@
         <v>74</v>
       </c>
       <c r="J10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K10" t="n">
         <v>73</v>
@@ -1057,7 +1057,7 @@
         <v>69</v>
       </c>
       <c r="J12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" t="n">
         <v>68</v>
@@ -2455,7 +2455,7 @@
         <v>181</v>
       </c>
       <c r="H39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I39" t="n">
         <v>180</v>
@@ -3241,7 +3241,7 @@
         <v>33</v>
       </c>
       <c r="J54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K54" t="n">
         <v>31</v>
@@ -3296,7 +3296,7 @@
         <v>97</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L55" t="n">
         <v>96</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F57" t="n">
         <v>147</v>
@@ -3409,7 +3409,7 @@
         <v>147</v>
       </c>
       <c r="N57" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>535</v>
+      </c>
+      <c r="F58" t="n">
         <v>531</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>530</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>525</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>523</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>519</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>518</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>516</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>512</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>511</v>
-      </c>
-      <c r="N58" t="n">
-        <v>510</v>
       </c>
     </row>
     <row r="59">
@@ -3926,7 +3926,7 @@
         <v>103</v>
       </c>
       <c r="M67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N67" t="n">
         <v>102</v>
@@ -4229,7 +4229,7 @@
         <v>78</v>
       </c>
       <c r="J73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K73" t="n">
         <v>77</v>
@@ -4709,7 +4709,7 @@
         <v>62</v>
       </c>
       <c r="N82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83">

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-16</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-07</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-06</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         <v>182</v>
       </c>
       <c r="K8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L8" t="n">
         <v>181</v>
@@ -901,10 +901,10 @@
         <v>131</v>
       </c>
       <c r="J9" t="n">
+        <v>131</v>
+      </c>
+      <c r="K9" t="n">
         <v>130</v>
-      </c>
-      <c r="K9" t="n">
-        <v>129</v>
       </c>
       <c r="L9" t="n">
         <v>129</v>
@@ -956,7 +956,7 @@
         <v>74</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L10" t="n">
         <v>73</v>
@@ -1060,7 +1060,7 @@
         <v>69</v>
       </c>
       <c r="K12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L12" t="n">
         <v>68</v>
@@ -2458,7 +2458,7 @@
         <v>181</v>
       </c>
       <c r="I39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J39" t="n">
         <v>180</v>
@@ -3244,7 +3244,7 @@
         <v>33</v>
       </c>
       <c r="K54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L54" t="n">
         <v>31</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F55" t="n">
         <v>97</v>
@@ -3299,7 +3299,7 @@
         <v>97</v>
       </c>
       <c r="L55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M55" t="n">
         <v>96</v>
@@ -3385,7 +3385,7 @@
         <v>148</v>
       </c>
       <c r="F57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>539</v>
+      </c>
+      <c r="F58" t="n">
         <v>535</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>531</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>530</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>525</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>523</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>519</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>518</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>516</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>512</v>
-      </c>
-      <c r="N58" t="n">
-        <v>511</v>
       </c>
     </row>
     <row r="59">
@@ -3929,7 +3929,7 @@
         <v>103</v>
       </c>
       <c r="N67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,7 @@
         <v>78</v>
       </c>
       <c r="K73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L73" t="n">
         <v>77</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-17</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-08</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-07</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
         <v>128</v>
@@ -855,7 +855,7 @@
         <v>182</v>
       </c>
       <c r="L8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M8" t="n">
         <v>181</v>
@@ -904,10 +904,10 @@
         <v>131</v>
       </c>
       <c r="K9" t="n">
+        <v>131</v>
+      </c>
+      <c r="L9" t="n">
         <v>130</v>
-      </c>
-      <c r="L9" t="n">
-        <v>129</v>
       </c>
       <c r="M9" t="n">
         <v>129</v>
@@ -959,7 +959,7 @@
         <v>74</v>
       </c>
       <c r="L10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M10" t="n">
         <v>73</v>
@@ -1063,7 +1063,7 @@
         <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M12" t="n">
         <v>68</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F39" t="n">
         <v>181</v>
@@ -2461,7 +2461,7 @@
         <v>181</v>
       </c>
       <c r="J39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K39" t="n">
         <v>180</v>
@@ -3247,7 +3247,7 @@
         <v>33</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M54" t="n">
         <v>31</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="E55" t="n">
+        <v>99</v>
+      </c>
+      <c r="F55" t="n">
         <v>98</v>
-      </c>
-      <c r="F55" t="n">
-        <v>97</v>
       </c>
       <c r="G55" t="n">
         <v>97</v>
@@ -3302,7 +3302,7 @@
         <v>97</v>
       </c>
       <c r="M55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N55" t="n">
         <v>96</v>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F57" t="n">
         <v>148</v>
       </c>
       <c r="G57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>544</v>
+      </c>
+      <c r="F58" t="n">
         <v>539</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>535</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>531</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>530</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>525</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>523</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>519</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>518</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>516</v>
-      </c>
-      <c r="N58" t="n">
-        <v>512</v>
       </c>
     </row>
     <row r="59">
@@ -4235,7 +4235,7 @@
         <v>78</v>
       </c>
       <c r="L73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M73" t="n">
         <v>77</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F78" t="n">
         <v>289</v>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="F91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-18</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-09</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-08</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
         <v>128</v>
@@ -858,7 +858,7 @@
         <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N8" t="n">
         <v>181</v>
@@ -907,10 +907,10 @@
         <v>131</v>
       </c>
       <c r="L9" t="n">
+        <v>131</v>
+      </c>
+      <c r="M9" t="n">
         <v>130</v>
-      </c>
-      <c r="M9" t="n">
-        <v>129</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -962,7 +962,7 @@
         <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
         <v>73</v>
@@ -1066,7 +1066,7 @@
         <v>69</v>
       </c>
       <c r="M12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N12" t="n">
         <v>68</v>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="E39" t="n">
+        <v>183</v>
+      </c>
+      <c r="F39" t="n">
         <v>182</v>
-      </c>
-      <c r="F39" t="n">
-        <v>181</v>
       </c>
       <c r="G39" t="n">
         <v>181</v>
@@ -2464,7 +2464,7 @@
         <v>181</v>
       </c>
       <c r="K39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L39" t="n">
         <v>180</v>
@@ -3250,7 +3250,7 @@
         <v>33</v>
       </c>
       <c r="M54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N54" t="n">
         <v>31</v>
@@ -3281,10 +3281,10 @@
         <v>99</v>
       </c>
       <c r="F55" t="n">
+        <v>99</v>
+      </c>
+      <c r="G55" t="n">
         <v>98</v>
-      </c>
-      <c r="G55" t="n">
-        <v>97</v>
       </c>
       <c r="H55" t="n">
         <v>97</v>
@@ -3305,7 +3305,7 @@
         <v>97</v>
       </c>
       <c r="N55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -3382,16 +3382,16 @@
         </is>
       </c>
       <c r="E57" t="n">
+        <v>150</v>
+      </c>
+      <c r="F57" t="n">
         <v>149</v>
-      </c>
-      <c r="F57" t="n">
-        <v>148</v>
       </c>
       <c r="G57" t="n">
         <v>148</v>
       </c>
       <c r="H57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>545</v>
+      </c>
+      <c r="F58" t="n">
         <v>544</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>539</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>535</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>531</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>530</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>525</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>523</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>519</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>518</v>
-      </c>
-      <c r="N58" t="n">
-        <v>516</v>
       </c>
     </row>
     <row r="59">
@@ -4238,7 +4238,7 @@
         <v>78</v>
       </c>
       <c r="M73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N73" t="n">
         <v>77</v>
@@ -4477,7 +4477,7 @@
         <v>290</v>
       </c>
       <c r="F78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G78" t="n">
         <v>289</v>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="E91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="F91" t="n">
         <v>3115</v>
-      </c>
-      <c r="F91" t="n">
-        <v>3114</v>
       </c>
       <c r="G91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-19</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-10</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-09</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         <v>129</v>
       </c>
       <c r="G7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H7" t="n">
         <v>128</v>
@@ -861,7 +861,7 @@
         <v>182</v>
       </c>
       <c r="N8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9">
@@ -910,10 +910,10 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
+        <v>131</v>
+      </c>
+      <c r="N9" t="n">
         <v>130</v>
-      </c>
-      <c r="N9" t="n">
-        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -965,7 +965,7 @@
         <v>74</v>
       </c>
       <c r="N10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -1069,7 +1069,7 @@
         <v>69</v>
       </c>
       <c r="N12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -2449,10 +2449,10 @@
         <v>183</v>
       </c>
       <c r="F39" t="n">
+        <v>183</v>
+      </c>
+      <c r="G39" t="n">
         <v>182</v>
-      </c>
-      <c r="G39" t="n">
-        <v>181</v>
       </c>
       <c r="H39" t="n">
         <v>181</v>
@@ -2467,7 +2467,7 @@
         <v>181</v>
       </c>
       <c r="L39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M39" t="n">
         <v>180</v>
@@ -3253,7 +3253,7 @@
         <v>33</v>
       </c>
       <c r="N54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -3284,10 +3284,10 @@
         <v>99</v>
       </c>
       <c r="G55" t="n">
+        <v>99</v>
+      </c>
+      <c r="H55" t="n">
         <v>98</v>
-      </c>
-      <c r="H55" t="n">
-        <v>97</v>
       </c>
       <c r="I55" t="n">
         <v>97</v>
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="E57" t="n">
+        <v>154</v>
+      </c>
+      <c r="F57" t="n">
         <v>150</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>149</v>
-      </c>
-      <c r="G57" t="n">
-        <v>148</v>
       </c>
       <c r="H57" t="n">
         <v>148</v>
       </c>
       <c r="I57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>548</v>
+      </c>
+      <c r="F58" t="n">
         <v>545</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>544</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>539</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>535</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>531</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>530</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>525</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>523</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>519</v>
-      </c>
-      <c r="N58" t="n">
-        <v>518</v>
       </c>
     </row>
     <row r="59">
@@ -4241,7 +4241,7 @@
         <v>78</v>
       </c>
       <c r="N73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
@@ -4480,7 +4480,7 @@
         <v>290</v>
       </c>
       <c r="G78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H78" t="n">
         <v>289</v>
@@ -5153,10 +5153,10 @@
         <v>3116</v>
       </c>
       <c r="F91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="G91" t="n">
         <v>3115</v>
-      </c>
-      <c r="G91" t="n">
-        <v>3114</v>
       </c>
       <c r="H91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-20</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-11</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-10</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         <v>129</v>
       </c>
       <c r="H7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I7" t="n">
         <v>128</v>
@@ -913,7 +913,7 @@
         <v>131</v>
       </c>
       <c r="N9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -2446,16 +2446,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F39" t="n">
         <v>183</v>
       </c>
       <c r="G39" t="n">
+        <v>183</v>
+      </c>
+      <c r="H39" t="n">
         <v>182</v>
-      </c>
-      <c r="H39" t="n">
-        <v>181</v>
       </c>
       <c r="I39" t="n">
         <v>181</v>
@@ -2470,7 +2470,7 @@
         <v>181</v>
       </c>
       <c r="M39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N39" t="n">
         <v>180</v>
@@ -3287,10 +3287,10 @@
         <v>99</v>
       </c>
       <c r="H55" t="n">
+        <v>99</v>
+      </c>
+      <c r="I55" t="n">
         <v>98</v>
-      </c>
-      <c r="I55" t="n">
-        <v>97</v>
       </c>
       <c r="J55" t="n">
         <v>97</v>
@@ -3385,19 +3385,19 @@
         <v>154</v>
       </c>
       <c r="F57" t="n">
+        <v>154</v>
+      </c>
+      <c r="G57" t="n">
         <v>150</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>149</v>
-      </c>
-      <c r="H57" t="n">
-        <v>148</v>
       </c>
       <c r="I57" t="n">
         <v>148</v>
       </c>
       <c r="J57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>549</v>
+      </c>
+      <c r="F58" t="n">
         <v>548</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>545</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>544</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>539</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>535</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>531</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>530</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>525</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>523</v>
-      </c>
-      <c r="N58" t="n">
-        <v>519</v>
       </c>
     </row>
     <row r="59">
@@ -4483,7 +4483,7 @@
         <v>290</v>
       </c>
       <c r="H78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I78" t="n">
         <v>289</v>
@@ -5156,10 +5156,10 @@
         <v>3116</v>
       </c>
       <c r="G91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="H91" t="n">
         <v>3115</v>
-      </c>
-      <c r="H91" t="n">
-        <v>3114</v>
       </c>
       <c r="I91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-22</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-12</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-11</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
         <v>129</v>
       </c>
       <c r="I7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J7" t="n">
         <v>128</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
         <v>39</v>
@@ -2449,16 +2449,16 @@
         <v>182</v>
       </c>
       <c r="F39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G39" t="n">
         <v>183</v>
       </c>
       <c r="H39" t="n">
+        <v>183</v>
+      </c>
+      <c r="I39" t="n">
         <v>182</v>
-      </c>
-      <c r="I39" t="n">
-        <v>181</v>
       </c>
       <c r="J39" t="n">
         <v>181</v>
@@ -2473,7 +2473,7 @@
         <v>181</v>
       </c>
       <c r="N39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
@@ -3290,10 +3290,10 @@
         <v>99</v>
       </c>
       <c r="I55" t="n">
+        <v>99</v>
+      </c>
+      <c r="J55" t="n">
         <v>98</v>
-      </c>
-      <c r="J55" t="n">
-        <v>97</v>
       </c>
       <c r="K55" t="n">
         <v>97</v>
@@ -3382,25 +3382,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" t="n">
         <v>154</v>
       </c>
       <c r="G57" t="n">
+        <v>154</v>
+      </c>
+      <c r="H57" t="n">
         <v>150</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>149</v>
-      </c>
-      <c r="I57" t="n">
-        <v>148</v>
       </c>
       <c r="J57" t="n">
         <v>148</v>
       </c>
       <c r="K57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>552</v>
+      </c>
+      <c r="F58" t="n">
         <v>549</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>548</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>545</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>544</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>539</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>535</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>531</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>530</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>525</v>
-      </c>
-      <c r="N58" t="n">
-        <v>523</v>
       </c>
     </row>
     <row r="59">
@@ -4486,7 +4486,7 @@
         <v>290</v>
       </c>
       <c r="I78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J78" t="n">
         <v>289</v>
@@ -5159,10 +5159,10 @@
         <v>3116</v>
       </c>
       <c r="H91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="I91" t="n">
         <v>3115</v>
-      </c>
-      <c r="I91" t="n">
-        <v>3114</v>
       </c>
       <c r="J91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-24</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-13</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-12</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>129</v>
@@ -797,7 +797,7 @@
         <v>129</v>
       </c>
       <c r="J7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K7" t="n">
         <v>128</v>
@@ -1721,7 +1721,7 @@
         <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
         <v>39</v>
@@ -2452,16 +2452,16 @@
         <v>182</v>
       </c>
       <c r="G39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H39" t="n">
         <v>183</v>
       </c>
       <c r="I39" t="n">
+        <v>183</v>
+      </c>
+      <c r="J39" t="n">
         <v>182</v>
-      </c>
-      <c r="J39" t="n">
-        <v>181</v>
       </c>
       <c r="K39" t="n">
         <v>181</v>
@@ -3293,10 +3293,10 @@
         <v>99</v>
       </c>
       <c r="J55" t="n">
+        <v>99</v>
+      </c>
+      <c r="K55" t="n">
         <v>98</v>
-      </c>
-      <c r="K55" t="n">
-        <v>97</v>
       </c>
       <c r="L55" t="n">
         <v>97</v>
@@ -3382,28 +3382,28 @@
         </is>
       </c>
       <c r="E57" t="n">
+        <v>154</v>
+      </c>
+      <c r="F57" t="n">
         <v>153</v>
-      </c>
-      <c r="F57" t="n">
-        <v>154</v>
       </c>
       <c r="G57" t="n">
         <v>154</v>
       </c>
       <c r="H57" t="n">
+        <v>154</v>
+      </c>
+      <c r="I57" t="n">
         <v>150</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>149</v>
-      </c>
-      <c r="J57" t="n">
-        <v>148</v>
       </c>
       <c r="K57" t="n">
         <v>148</v>
       </c>
       <c r="L57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>561</v>
+      </c>
+      <c r="F58" t="n">
         <v>552</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>549</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>548</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>545</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>544</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>539</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>535</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>531</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>530</v>
-      </c>
-      <c r="N58" t="n">
-        <v>525</v>
       </c>
     </row>
     <row r="59">
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F73" t="n">
         <v>78</v>
@@ -4489,7 +4489,7 @@
         <v>290</v>
       </c>
       <c r="J78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K78" t="n">
         <v>289</v>
@@ -5162,10 +5162,10 @@
         <v>3116</v>
       </c>
       <c r="I91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="J91" t="n">
         <v>3115</v>
-      </c>
-      <c r="J91" t="n">
-        <v>3114</v>
       </c>
       <c r="K91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-25</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-14</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-13</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
         <v>129</v>
@@ -800,7 +800,7 @@
         <v>129</v>
       </c>
       <c r="K7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L7" t="n">
         <v>128</v>
@@ -1724,7 +1724,7 @@
         <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" t="n">
         <v>39</v>
@@ -2455,16 +2455,16 @@
         <v>182</v>
       </c>
       <c r="H39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I39" t="n">
         <v>183</v>
       </c>
       <c r="J39" t="n">
+        <v>183</v>
+      </c>
+      <c r="K39" t="n">
         <v>182</v>
-      </c>
-      <c r="K39" t="n">
-        <v>181</v>
       </c>
       <c r="L39" t="n">
         <v>181</v>
@@ -3296,10 +3296,10 @@
         <v>99</v>
       </c>
       <c r="K55" t="n">
+        <v>99</v>
+      </c>
+      <c r="L55" t="n">
         <v>98</v>
-      </c>
-      <c r="L55" t="n">
-        <v>97</v>
       </c>
       <c r="M55" t="n">
         <v>97</v>
@@ -3385,28 +3385,28 @@
         <v>154</v>
       </c>
       <c r="F57" t="n">
+        <v>154</v>
+      </c>
+      <c r="G57" t="n">
         <v>153</v>
-      </c>
-      <c r="G57" t="n">
-        <v>154</v>
       </c>
       <c r="H57" t="n">
         <v>154</v>
       </c>
       <c r="I57" t="n">
+        <v>154</v>
+      </c>
+      <c r="J57" t="n">
         <v>150</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>149</v>
-      </c>
-      <c r="K57" t="n">
-        <v>148</v>
       </c>
       <c r="L57" t="n">
         <v>148</v>
       </c>
       <c r="M57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N57" t="n">
         <v>147</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>563</v>
+      </c>
+      <c r="F58" t="n">
         <v>561</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>552</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>549</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>548</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>545</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>544</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>539</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>535</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>531</v>
-      </c>
-      <c r="N58" t="n">
-        <v>530</v>
       </c>
     </row>
     <row r="59">
@@ -4217,7 +4217,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G73" t="n">
         <v>78</v>
@@ -4492,7 +4492,7 @@
         <v>290</v>
       </c>
       <c r="K78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L78" t="n">
         <v>289</v>
@@ -5165,10 +5165,10 @@
         <v>3116</v>
       </c>
       <c r="J91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="K91" t="n">
         <v>3115</v>
-      </c>
-      <c r="K91" t="n">
-        <v>3114</v>
       </c>
       <c r="L91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-26</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-15</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         <v>130</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H7" t="n">
         <v>129</v>
@@ -803,7 +803,7 @@
         <v>129</v>
       </c>
       <c r="L7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M7" t="n">
         <v>128</v>
@@ -1727,7 +1727,7 @@
         <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I25" t="n">
         <v>39</v>
@@ -2458,16 +2458,16 @@
         <v>182</v>
       </c>
       <c r="I39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J39" t="n">
         <v>183</v>
       </c>
       <c r="K39" t="n">
+        <v>183</v>
+      </c>
+      <c r="L39" t="n">
         <v>182</v>
-      </c>
-      <c r="L39" t="n">
-        <v>181</v>
       </c>
       <c r="M39" t="n">
         <v>181</v>
@@ -3299,10 +3299,10 @@
         <v>99</v>
       </c>
       <c r="L55" t="n">
+        <v>99</v>
+      </c>
+      <c r="M55" t="n">
         <v>98</v>
-      </c>
-      <c r="M55" t="n">
-        <v>97</v>
       </c>
       <c r="N55" t="n">
         <v>97</v>
@@ -3382,34 +3382,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F57" t="n">
         <v>154</v>
       </c>
       <c r="G57" t="n">
+        <v>154</v>
+      </c>
+      <c r="H57" t="n">
         <v>153</v>
-      </c>
-      <c r="H57" t="n">
-        <v>154</v>
       </c>
       <c r="I57" t="n">
         <v>154</v>
       </c>
       <c r="J57" t="n">
+        <v>154</v>
+      </c>
+      <c r="K57" t="n">
         <v>150</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>149</v>
-      </c>
-      <c r="L57" t="n">
-        <v>148</v>
       </c>
       <c r="M57" t="n">
         <v>148</v>
       </c>
       <c r="N57" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>565</v>
+      </c>
+      <c r="F58" t="n">
         <v>563</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>561</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>552</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>549</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>548</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>545</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>544</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>539</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>535</v>
-      </c>
-      <c r="N58" t="n">
-        <v>531</v>
       </c>
     </row>
     <row r="59">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F59" t="n">
         <v>46</v>
@@ -4220,7 +4220,7 @@
         <v>79</v>
       </c>
       <c r="G73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H73" t="n">
         <v>78</v>
@@ -4495,7 +4495,7 @@
         <v>290</v>
       </c>
       <c r="L78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M78" t="n">
         <v>289</v>
@@ -5168,10 +5168,10 @@
         <v>3116</v>
       </c>
       <c r="K91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="L91" t="n">
         <v>3115</v>
-      </c>
-      <c r="L91" t="n">
-        <v>3114</v>
       </c>
       <c r="M91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-27</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-16</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-15</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="n">
         <v>101</v>
@@ -791,7 +791,7 @@
         <v>130</v>
       </c>
       <c r="H7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I7" t="n">
         <v>129</v>
@@ -806,7 +806,7 @@
         <v>129</v>
       </c>
       <c r="M7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N7" t="n">
         <v>128</v>
@@ -1730,7 +1730,7 @@
         <v>40</v>
       </c>
       <c r="I25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J25" t="n">
         <v>39</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F33" t="n">
         <v>65</v>
@@ -2461,16 +2461,16 @@
         <v>182</v>
       </c>
       <c r="J39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K39" t="n">
         <v>183</v>
       </c>
       <c r="L39" t="n">
+        <v>183</v>
+      </c>
+      <c r="M39" t="n">
         <v>182</v>
-      </c>
-      <c r="M39" t="n">
-        <v>181</v>
       </c>
       <c r="N39" t="n">
         <v>181</v>
@@ -3302,10 +3302,10 @@
         <v>99</v>
       </c>
       <c r="M55" t="n">
+        <v>99</v>
+      </c>
+      <c r="N55" t="n">
         <v>98</v>
-      </c>
-      <c r="N55" t="n">
-        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -3382,31 +3382,31 @@
         </is>
       </c>
       <c r="E57" t="n">
+        <v>156</v>
+      </c>
+      <c r="F57" t="n">
         <v>155</v>
-      </c>
-      <c r="F57" t="n">
-        <v>154</v>
       </c>
       <c r="G57" t="n">
         <v>154</v>
       </c>
       <c r="H57" t="n">
+        <v>154</v>
+      </c>
+      <c r="I57" t="n">
         <v>153</v>
-      </c>
-      <c r="I57" t="n">
-        <v>154</v>
       </c>
       <c r="J57" t="n">
         <v>154</v>
       </c>
       <c r="K57" t="n">
+        <v>154</v>
+      </c>
+      <c r="L57" t="n">
         <v>150</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>149</v>
-      </c>
-      <c r="M57" t="n">
-        <v>148</v>
       </c>
       <c r="N57" t="n">
         <v>148</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>568</v>
+      </c>
+      <c r="F58" t="n">
         <v>565</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>563</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>561</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>552</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>549</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>548</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>545</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>544</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>539</v>
-      </c>
-      <c r="N58" t="n">
-        <v>535</v>
       </c>
     </row>
     <row r="59">
@@ -3489,7 +3489,7 @@
         <v>47</v>
       </c>
       <c r="F59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G59" t="n">
         <v>46</v>
@@ -4223,7 +4223,7 @@
         <v>79</v>
       </c>
       <c r="H73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I73" t="n">
         <v>78</v>
@@ -4498,7 +4498,7 @@
         <v>290</v>
       </c>
       <c r="M78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N78" t="n">
         <v>289</v>
@@ -5171,10 +5171,10 @@
         <v>3116</v>
       </c>
       <c r="L91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M91" t="n">
         <v>3115</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3114</v>
       </c>
       <c r="N91" t="n">
         <v>3114</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-28</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-17</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-16</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         <v>102</v>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
         <v>101</v>
@@ -794,7 +794,7 @@
         <v>130</v>
       </c>
       <c r="I7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J7" t="n">
         <v>129</v>
@@ -809,7 +809,7 @@
         <v>129</v>
       </c>
       <c r="N7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" t="n">
         <v>88</v>
@@ -1733,7 +1733,7 @@
         <v>40</v>
       </c>
       <c r="J25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K25" t="n">
         <v>39</v>
@@ -2137,7 +2137,7 @@
         <v>66</v>
       </c>
       <c r="F33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G33" t="n">
         <v>65</v>
@@ -2464,16 +2464,16 @@
         <v>182</v>
       </c>
       <c r="K39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L39" t="n">
         <v>183</v>
       </c>
       <c r="M39" t="n">
+        <v>183</v>
+      </c>
+      <c r="N39" t="n">
         <v>182</v>
-      </c>
-      <c r="N39" t="n">
-        <v>181</v>
       </c>
     </row>
     <row r="40">
@@ -3305,7 +3305,7 @@
         <v>99</v>
       </c>
       <c r="N55" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56">
@@ -3385,31 +3385,31 @@
         <v>156</v>
       </c>
       <c r="F57" t="n">
+        <v>156</v>
+      </c>
+      <c r="G57" t="n">
         <v>155</v>
-      </c>
-      <c r="G57" t="n">
-        <v>154</v>
       </c>
       <c r="H57" t="n">
         <v>154</v>
       </c>
       <c r="I57" t="n">
+        <v>154</v>
+      </c>
+      <c r="J57" t="n">
         <v>153</v>
-      </c>
-      <c r="J57" t="n">
-        <v>154</v>
       </c>
       <c r="K57" t="n">
         <v>154</v>
       </c>
       <c r="L57" t="n">
+        <v>154</v>
+      </c>
+      <c r="M57" t="n">
         <v>150</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>149</v>
-      </c>
-      <c r="N57" t="n">
-        <v>148</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>573</v>
+      </c>
+      <c r="F58" t="n">
         <v>568</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>565</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>563</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>561</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>552</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>549</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>548</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>545</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>544</v>
-      </c>
-      <c r="N58" t="n">
-        <v>539</v>
       </c>
     </row>
     <row r="59">
@@ -3492,7 +3492,7 @@
         <v>47</v>
       </c>
       <c r="G59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" t="n">
         <v>46</v>
@@ -4226,7 +4226,7 @@
         <v>79</v>
       </c>
       <c r="I73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J73" t="n">
         <v>78</v>
@@ -4501,7 +4501,7 @@
         <v>290</v>
       </c>
       <c r="N78" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="79">
@@ -5174,10 +5174,10 @@
         <v>3116</v>
       </c>
       <c r="M91" t="n">
+        <v>3116</v>
+      </c>
+      <c r="N91" t="n">
         <v>3115</v>
-      </c>
-      <c r="N91" t="n">
-        <v>3114</v>
       </c>
     </row>
     <row r="92">

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-29</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-18</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-17</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
         <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
         <v>101</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
         <v>130</v>
@@ -797,7 +797,7 @@
         <v>130</v>
       </c>
       <c r="J7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K7" t="n">
         <v>129</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
         <v>56</v>
@@ -1617,7 +1617,7 @@
         <v>89</v>
       </c>
       <c r="F23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G23" t="n">
         <v>88</v>
@@ -1736,7 +1736,7 @@
         <v>40</v>
       </c>
       <c r="K25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L25" t="n">
         <v>39</v>
@@ -2140,7 +2140,7 @@
         <v>66</v>
       </c>
       <c r="G33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H33" t="n">
         <v>65</v>
@@ -2467,13 +2467,13 @@
         <v>182</v>
       </c>
       <c r="L39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M39" t="n">
         <v>183</v>
       </c>
       <c r="N39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40">
@@ -3388,28 +3388,28 @@
         <v>156</v>
       </c>
       <c r="G57" t="n">
+        <v>156</v>
+      </c>
+      <c r="H57" t="n">
         <v>155</v>
-      </c>
-      <c r="H57" t="n">
-        <v>154</v>
       </c>
       <c r="I57" t="n">
         <v>154</v>
       </c>
       <c r="J57" t="n">
+        <v>154</v>
+      </c>
+      <c r="K57" t="n">
         <v>153</v>
-      </c>
-      <c r="K57" t="n">
-        <v>154</v>
       </c>
       <c r="L57" t="n">
         <v>154</v>
       </c>
       <c r="M57" t="n">
+        <v>154</v>
+      </c>
+      <c r="N57" t="n">
         <v>150</v>
-      </c>
-      <c r="N57" t="n">
-        <v>149</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>575</v>
+      </c>
+      <c r="F58" t="n">
         <v>573</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>568</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>565</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>563</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>561</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>552</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>549</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>548</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>545</v>
-      </c>
-      <c r="N58" t="n">
-        <v>544</v>
       </c>
     </row>
     <row r="59">
@@ -3495,7 +3495,7 @@
         <v>47</v>
       </c>
       <c r="H59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I59" t="n">
         <v>46</v>
@@ -4229,7 +4229,7 @@
         <v>79</v>
       </c>
       <c r="J73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K73" t="n">
         <v>78</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F90" t="n">
         <v>210</v>
@@ -5177,7 +5177,7 @@
         <v>3116</v>
       </c>
       <c r="N91" t="n">
-        <v>3115</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="92">

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-09-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-19</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-18</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I2" t="n">
         <v>101</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>132</v>
+      </c>
+      <c r="F7" t="n">
         <v>131</v>
-      </c>
-      <c r="F7" t="n">
-        <v>130</v>
       </c>
       <c r="G7" t="n">
         <v>130</v>
@@ -800,7 +800,7 @@
         <v>130</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L7" t="n">
         <v>129</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
         <v>90</v>
@@ -1409,7 +1409,7 @@
         <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
         <v>56</v>
@@ -1620,7 +1620,7 @@
         <v>89</v>
       </c>
       <c r="G23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="n">
         <v>88</v>
@@ -1739,7 +1739,7 @@
         <v>40</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M25" t="n">
         <v>39</v>
@@ -2143,7 +2143,7 @@
         <v>66</v>
       </c>
       <c r="H33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33" t="n">
         <v>65</v>
@@ -2470,7 +2470,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N39" t="n">
         <v>183</v>
@@ -3391,25 +3391,25 @@
         <v>156</v>
       </c>
       <c r="H57" t="n">
+        <v>156</v>
+      </c>
+      <c r="I57" t="n">
         <v>155</v>
-      </c>
-      <c r="I57" t="n">
-        <v>154</v>
       </c>
       <c r="J57" t="n">
         <v>154</v>
       </c>
       <c r="K57" t="n">
+        <v>154</v>
+      </c>
+      <c r="L57" t="n">
         <v>153</v>
-      </c>
-      <c r="L57" t="n">
-        <v>154</v>
       </c>
       <c r="M57" t="n">
         <v>154</v>
       </c>
       <c r="N57" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>577</v>
+      </c>
+      <c r="F58" t="n">
         <v>575</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>573</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>568</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>565</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>563</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>561</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>552</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>549</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>548</v>
-      </c>
-      <c r="N58" t="n">
-        <v>545</v>
       </c>
     </row>
     <row r="59">
@@ -3498,7 +3498,7 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J59" t="n">
         <v>46</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F63" t="n">
         <v>53</v>
@@ -4232,7 +4232,7 @@
         <v>79</v>
       </c>
       <c r="K73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L73" t="n">
         <v>78</v>
@@ -5101,7 +5101,7 @@
         <v>211</v>
       </c>
       <c r="F90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G90" t="n">
         <v>210</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-01</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-20</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-19</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
         <v>102</v>
       </c>
       <c r="I2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J2" t="n">
         <v>101</v>
@@ -785,10 +785,10 @@
         <v>132</v>
       </c>
       <c r="F7" t="n">
+        <v>132</v>
+      </c>
+      <c r="G7" t="n">
         <v>131</v>
-      </c>
-      <c r="G7" t="n">
-        <v>130</v>
       </c>
       <c r="H7" t="n">
         <v>130</v>
@@ -803,7 +803,7 @@
         <v>130</v>
       </c>
       <c r="L7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M7" t="n">
         <v>129</v>
@@ -993,7 +993,7 @@
         <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
         <v>90</v>
@@ -1412,7 +1412,7 @@
         <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" t="n">
         <v>56</v>
@@ -1623,7 +1623,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I23" t="n">
         <v>88</v>
@@ -1742,7 +1742,7 @@
         <v>40</v>
       </c>
       <c r="M25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N25" t="n">
         <v>39</v>
@@ -2146,7 +2146,7 @@
         <v>66</v>
       </c>
       <c r="I33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J33" t="n">
         <v>65</v>
@@ -2473,7 +2473,7 @@
         <v>182</v>
       </c>
       <c r="N39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40">
@@ -3394,19 +3394,19 @@
         <v>156</v>
       </c>
       <c r="I57" t="n">
+        <v>156</v>
+      </c>
+      <c r="J57" t="n">
         <v>155</v>
-      </c>
-      <c r="J57" t="n">
-        <v>154</v>
       </c>
       <c r="K57" t="n">
         <v>154</v>
       </c>
       <c r="L57" t="n">
+        <v>154</v>
+      </c>
+      <c r="M57" t="n">
         <v>153</v>
-      </c>
-      <c r="M57" t="n">
-        <v>154</v>
       </c>
       <c r="N57" t="n">
         <v>154</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>579</v>
+      </c>
+      <c r="F58" t="n">
         <v>577</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>575</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>573</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>568</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>565</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>563</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>561</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>552</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>549</v>
-      </c>
-      <c r="N58" t="n">
-        <v>548</v>
       </c>
     </row>
     <row r="59">
@@ -3501,7 +3501,7 @@
         <v>47</v>
       </c>
       <c r="J59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K59" t="n">
         <v>46</v>
@@ -3697,7 +3697,7 @@
         <v>54</v>
       </c>
       <c r="F63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63" t="n">
         <v>53</v>
@@ -4235,7 +4235,7 @@
         <v>79</v>
       </c>
       <c r="L73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M73" t="n">
         <v>78</v>
@@ -5104,7 +5104,7 @@
         <v>211</v>
       </c>
       <c r="G90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H90" t="n">
         <v>210</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-22</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-20</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         <v>102</v>
       </c>
       <c r="J2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
         <v>101</v>
@@ -788,10 +788,10 @@
         <v>132</v>
       </c>
       <c r="G7" t="n">
+        <v>132</v>
+      </c>
+      <c r="H7" t="n">
         <v>131</v>
-      </c>
-      <c r="H7" t="n">
-        <v>130</v>
       </c>
       <c r="I7" t="n">
         <v>130</v>
@@ -806,7 +806,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N7" t="n">
         <v>129</v>
@@ -996,7 +996,7 @@
         <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="n">
         <v>90</v>
@@ -1415,7 +1415,7 @@
         <v>57</v>
       </c>
       <c r="H19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I19" t="n">
         <v>56</v>
@@ -1626,7 +1626,7 @@
         <v>89</v>
       </c>
       <c r="I23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J23" t="n">
         <v>88</v>
@@ -1745,7 +1745,7 @@
         <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -2149,7 +2149,7 @@
         <v>66</v>
       </c>
       <c r="J33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K33" t="n">
         <v>65</v>
@@ -3397,19 +3397,19 @@
         <v>156</v>
       </c>
       <c r="J57" t="n">
+        <v>156</v>
+      </c>
+      <c r="K57" t="n">
         <v>155</v>
-      </c>
-      <c r="K57" t="n">
-        <v>154</v>
       </c>
       <c r="L57" t="n">
         <v>154</v>
       </c>
       <c r="M57" t="n">
+        <v>154</v>
+      </c>
+      <c r="N57" t="n">
         <v>153</v>
-      </c>
-      <c r="N57" t="n">
-        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>582</v>
+      </c>
+      <c r="F58" t="n">
         <v>579</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>577</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>575</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>573</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>568</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>565</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>563</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>561</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>552</v>
-      </c>
-      <c r="N58" t="n">
-        <v>549</v>
       </c>
     </row>
     <row r="59">
@@ -3504,7 +3504,7 @@
         <v>47</v>
       </c>
       <c r="K59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L59" t="n">
         <v>46</v>
@@ -3700,7 +3700,7 @@
         <v>54</v>
       </c>
       <c r="G63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H63" t="n">
         <v>53</v>
@@ -4238,7 +4238,7 @@
         <v>79</v>
       </c>
       <c r="M73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N73" t="n">
         <v>78</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F78" t="n">
         <v>290</v>
@@ -5107,7 +5107,7 @@
         <v>211</v>
       </c>
       <c r="H90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I90" t="n">
         <v>210</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-03</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-24</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-22</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L2" t="n">
         <v>101</v>
@@ -791,10 +791,10 @@
         <v>132</v>
       </c>
       <c r="H7" t="n">
+        <v>132</v>
+      </c>
+      <c r="I7" t="n">
         <v>131</v>
-      </c>
-      <c r="I7" t="n">
-        <v>130</v>
       </c>
       <c r="J7" t="n">
         <v>130</v>
@@ -809,7 +809,7 @@
         <v>130</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -999,7 +999,7 @@
         <v>91</v>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" t="n">
         <v>90</v>
@@ -1418,7 +1418,7 @@
         <v>57</v>
       </c>
       <c r="I19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J19" t="n">
         <v>56</v>
@@ -1629,7 +1629,7 @@
         <v>89</v>
       </c>
       <c r="J23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="n">
         <v>88</v>
@@ -2152,7 +2152,7 @@
         <v>66</v>
       </c>
       <c r="K33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L33" t="n">
         <v>65</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F57" t="n">
         <v>156</v>
@@ -3400,16 +3400,16 @@
         <v>156</v>
       </c>
       <c r="K57" t="n">
+        <v>156</v>
+      </c>
+      <c r="L57" t="n">
         <v>155</v>
-      </c>
-      <c r="L57" t="n">
-        <v>154</v>
       </c>
       <c r="M57" t="n">
         <v>154</v>
       </c>
       <c r="N57" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>584</v>
+      </c>
+      <c r="F58" t="n">
         <v>582</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>579</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>577</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>575</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>573</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>568</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>565</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>563</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>561</v>
-      </c>
-      <c r="N58" t="n">
-        <v>552</v>
       </c>
     </row>
     <row r="59">
@@ -3507,7 +3507,7 @@
         <v>47</v>
       </c>
       <c r="L59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M59" t="n">
         <v>46</v>
@@ -3703,7 +3703,7 @@
         <v>54</v>
       </c>
       <c r="H63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I63" t="n">
         <v>53</v>
@@ -4241,7 +4241,7 @@
         <v>79</v>
       </c>
       <c r="N73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -4477,7 +4477,7 @@
         <v>291</v>
       </c>
       <c r="F78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G78" t="n">
         <v>290</v>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F83" t="n">
         <v>222</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F89" t="n">
         <v>250</v>
@@ -5110,7 +5110,7 @@
         <v>211</v>
       </c>
       <c r="I90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J90" t="n">
         <v>210</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-04</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-25</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-24</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
         <v>102</v>
       </c>
       <c r="L2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M2" t="n">
         <v>101</v>
@@ -794,10 +794,10 @@
         <v>132</v>
       </c>
       <c r="I7" t="n">
+        <v>132</v>
+      </c>
+      <c r="J7" t="n">
         <v>131</v>
-      </c>
-      <c r="J7" t="n">
-        <v>130</v>
       </c>
       <c r="K7" t="n">
         <v>130</v>
@@ -1002,7 +1002,7 @@
         <v>91</v>
       </c>
       <c r="I11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J11" t="n">
         <v>90</v>
@@ -1421,7 +1421,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K19" t="n">
         <v>56</v>
@@ -1632,7 +1632,7 @@
         <v>89</v>
       </c>
       <c r="K23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L23" t="n">
         <v>88</v>
@@ -2155,7 +2155,7 @@
         <v>66</v>
       </c>
       <c r="L33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
         <v>65</v>
@@ -3385,7 +3385,7 @@
         <v>158</v>
       </c>
       <c r="F57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G57" t="n">
         <v>156</v>
@@ -3403,10 +3403,10 @@
         <v>156</v>
       </c>
       <c r="L57" t="n">
+        <v>156</v>
+      </c>
+      <c r="M57" t="n">
         <v>155</v>
-      </c>
-      <c r="M57" t="n">
-        <v>154</v>
       </c>
       <c r="N57" t="n">
         <v>154</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>585</v>
+      </c>
+      <c r="F58" t="n">
         <v>584</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>582</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>579</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>577</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>575</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>573</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>568</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>565</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>563</v>
-      </c>
-      <c r="N58" t="n">
-        <v>561</v>
       </c>
     </row>
     <row r="59">
@@ -3510,7 +3510,7 @@
         <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N59" t="n">
         <v>46</v>
@@ -3706,7 +3706,7 @@
         <v>54</v>
       </c>
       <c r="I63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J63" t="n">
         <v>53</v>
@@ -4480,7 +4480,7 @@
         <v>291</v>
       </c>
       <c r="G78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H78" t="n">
         <v>290</v>
@@ -4737,7 +4737,7 @@
         <v>223</v>
       </c>
       <c r="F83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G83" t="n">
         <v>222</v>
@@ -5049,7 +5049,7 @@
         <v>251</v>
       </c>
       <c r="F89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G89" t="n">
         <v>250</v>
@@ -5113,7 +5113,7 @@
         <v>211</v>
       </c>
       <c r="J90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K90" t="n">
         <v>210</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-06</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-26</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-25</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N2" t="n">
         <v>101</v>
@@ -797,10 +797,10 @@
         <v>132</v>
       </c>
       <c r="J7" t="n">
+        <v>132</v>
+      </c>
+      <c r="K7" t="n">
         <v>131</v>
-      </c>
-      <c r="K7" t="n">
-        <v>130</v>
       </c>
       <c r="L7" t="n">
         <v>130</v>
@@ -1005,7 +1005,7 @@
         <v>91</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="n">
         <v>90</v>
@@ -1424,7 +1424,7 @@
         <v>57</v>
       </c>
       <c r="K19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L19" t="n">
         <v>56</v>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
@@ -1635,7 +1635,7 @@
         <v>89</v>
       </c>
       <c r="L23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M23" t="n">
         <v>88</v>
@@ -2158,7 +2158,7 @@
         <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N33" t="n">
         <v>65</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F49" t="n">
         <v>401</v>
@@ -3388,7 +3388,7 @@
         <v>158</v>
       </c>
       <c r="G57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H57" t="n">
         <v>156</v>
@@ -3406,10 +3406,10 @@
         <v>156</v>
       </c>
       <c r="M57" t="n">
+        <v>156</v>
+      </c>
+      <c r="N57" t="n">
         <v>155</v>
-      </c>
-      <c r="N57" t="n">
-        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>592</v>
+      </c>
+      <c r="F58" t="n">
         <v>585</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>584</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>582</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>579</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>577</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>575</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>573</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>568</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>565</v>
-      </c>
-      <c r="N58" t="n">
-        <v>563</v>
       </c>
     </row>
     <row r="59">
@@ -3513,7 +3513,7 @@
         <v>47</v>
       </c>
       <c r="N59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -3709,7 +3709,7 @@
         <v>54</v>
       </c>
       <c r="J63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
         <v>53</v>
@@ -4483,7 +4483,7 @@
         <v>291</v>
       </c>
       <c r="H78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I78" t="n">
         <v>290</v>
@@ -4740,7 +4740,7 @@
         <v>223</v>
       </c>
       <c r="G83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H83" t="n">
         <v>222</v>
@@ -5052,7 +5052,7 @@
         <v>251</v>
       </c>
       <c r="G89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H89" t="n">
         <v>250</v>
@@ -5116,7 +5116,7 @@
         <v>211</v>
       </c>
       <c r="K90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L90" t="n">
         <v>210</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-07</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-27</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-26</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>102</v>
       </c>
       <c r="N2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -800,10 +800,10 @@
         <v>132</v>
       </c>
       <c r="K7" t="n">
+        <v>132</v>
+      </c>
+      <c r="L7" t="n">
         <v>131</v>
-      </c>
-      <c r="L7" t="n">
-        <v>130</v>
       </c>
       <c r="M7" t="n">
         <v>130</v>
@@ -1008,7 +1008,7 @@
         <v>91</v>
       </c>
       <c r="K11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" t="n">
         <v>90</v>
@@ -1427,7 +1427,7 @@
         <v>57</v>
       </c>
       <c r="L19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M19" t="n">
         <v>56</v>
@@ -1513,7 +1513,7 @@
         <v>34</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
         <v>33</v>
@@ -1638,7 +1638,7 @@
         <v>89</v>
       </c>
       <c r="M23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N23" t="n">
         <v>88</v>
@@ -2161,7 +2161,7 @@
         <v>66</v>
       </c>
       <c r="N33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34">
@@ -2969,7 +2969,7 @@
         <v>402</v>
       </c>
       <c r="F49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G49" t="n">
         <v>401</v>
@@ -3391,7 +3391,7 @@
         <v>158</v>
       </c>
       <c r="H57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I57" t="n">
         <v>156</v>
@@ -3409,7 +3409,7 @@
         <v>156</v>
       </c>
       <c r="N57" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>598</v>
+      </c>
+      <c r="F58" t="n">
         <v>592</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>585</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>584</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>582</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>579</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>577</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>575</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>573</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>568</v>
-      </c>
-      <c r="N58" t="n">
-        <v>565</v>
       </c>
     </row>
     <row r="59">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F59" t="n">
         <v>47</v>
@@ -3712,7 +3712,7 @@
         <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L63" t="n">
         <v>53</v>
@@ -4486,7 +4486,7 @@
         <v>291</v>
       </c>
       <c r="I78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J78" t="n">
         <v>290</v>
@@ -4743,7 +4743,7 @@
         <v>223</v>
       </c>
       <c r="H83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I83" t="n">
         <v>222</v>
@@ -5055,7 +5055,7 @@
         <v>251</v>
       </c>
       <c r="H89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I89" t="n">
         <v>250</v>
@@ -5119,7 +5119,7 @@
         <v>211</v>
       </c>
       <c r="L90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M90" t="n">
         <v>210</v>
@@ -5309,7 +5309,7 @@
         <v>842</v>
       </c>
       <c r="F94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-08</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-28</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-27</t>
         </is>
       </c>
     </row>
@@ -803,10 +803,10 @@
         <v>132</v>
       </c>
       <c r="L7" t="n">
+        <v>132</v>
+      </c>
+      <c r="M7" t="n">
         <v>131</v>
-      </c>
-      <c r="M7" t="n">
-        <v>130</v>
       </c>
       <c r="N7" t="n">
         <v>130</v>
@@ -1011,7 +1011,7 @@
         <v>91</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M11" t="n">
         <v>90</v>
@@ -1430,7 +1430,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N19" t="n">
         <v>56</v>
@@ -1516,7 +1516,7 @@
         <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" t="n">
         <v>33</v>
@@ -1641,7 +1641,7 @@
         <v>89</v>
       </c>
       <c r="N23" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F46" t="n">
         <v>287</v>
@@ -2972,7 +2972,7 @@
         <v>402</v>
       </c>
       <c r="G49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H49" t="n">
         <v>401</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F57" t="n">
         <v>158</v>
@@ -3394,7 +3394,7 @@
         <v>158</v>
       </c>
       <c r="I57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J57" t="n">
         <v>156</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>605</v>
+      </c>
+      <c r="F58" t="n">
         <v>598</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>592</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>585</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>584</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>582</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>579</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>577</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>575</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>573</v>
-      </c>
-      <c r="N58" t="n">
-        <v>568</v>
       </c>
     </row>
     <row r="59">
@@ -3489,7 +3489,7 @@
         <v>48</v>
       </c>
       <c r="F59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G59" t="n">
         <v>47</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F63" t="n">
         <v>54</v>
@@ -3715,7 +3715,7 @@
         <v>54</v>
       </c>
       <c r="L63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M63" t="n">
         <v>53</v>
@@ -4489,7 +4489,7 @@
         <v>291</v>
       </c>
       <c r="J78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K78" t="n">
         <v>290</v>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F83" t="n">
         <v>223</v>
@@ -4746,7 +4746,7 @@
         <v>223</v>
       </c>
       <c r="I83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J83" t="n">
         <v>222</v>
@@ -5058,7 +5058,7 @@
         <v>251</v>
       </c>
       <c r="I89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J89" t="n">
         <v>250</v>
@@ -5122,7 +5122,7 @@
         <v>211</v>
       </c>
       <c r="M90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N90" t="n">
         <v>210</v>
@@ -5312,7 +5312,7 @@
         <v>842</v>
       </c>
       <c r="G94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-09</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-29</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-28</t>
         </is>
       </c>
     </row>
@@ -806,10 +806,10 @@
         <v>132</v>
       </c>
       <c r="M7" t="n">
+        <v>132</v>
+      </c>
+      <c r="N7" t="n">
         <v>131</v>
-      </c>
-      <c r="N7" t="n">
-        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -1014,7 +1014,7 @@
         <v>91</v>
       </c>
       <c r="M11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N11" t="n">
         <v>90</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
         <v>69</v>
@@ -1433,7 +1433,7 @@
         <v>57</v>
       </c>
       <c r="N19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1519,7 +1519,7 @@
         <v>34</v>
       </c>
       <c r="H21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I21" t="n">
         <v>33</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F39" t="n">
         <v>182</v>
@@ -2813,7 +2813,7 @@
         <v>289</v>
       </c>
       <c r="F46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G46" t="n">
         <v>287</v>
@@ -2975,7 +2975,7 @@
         <v>402</v>
       </c>
       <c r="H49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I49" t="n">
         <v>401</v>
@@ -3385,7 +3385,7 @@
         <v>159</v>
       </c>
       <c r="F57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G57" t="n">
         <v>158</v>
@@ -3397,7 +3397,7 @@
         <v>158</v>
       </c>
       <c r="J57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K57" t="n">
         <v>156</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>608</v>
+      </c>
+      <c r="F58" t="n">
         <v>605</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>598</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>592</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>585</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>584</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>582</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>579</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>577</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>575</v>
-      </c>
-      <c r="N58" t="n">
-        <v>573</v>
       </c>
     </row>
     <row r="59">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
         <v>48</v>
       </c>
       <c r="G59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H59" t="n">
         <v>47</v>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
         <v>41</v>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="E63" t="n">
+        <v>56</v>
+      </c>
+      <c r="F63" t="n">
         <v>55</v>
-      </c>
-      <c r="F63" t="n">
-        <v>54</v>
       </c>
       <c r="G63" t="n">
         <v>54</v>
@@ -3718,7 +3718,7 @@
         <v>54</v>
       </c>
       <c r="M63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N63" t="n">
         <v>53</v>
@@ -4492,7 +4492,7 @@
         <v>291</v>
       </c>
       <c r="K78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L78" t="n">
         <v>290</v>
@@ -4737,7 +4737,7 @@
         <v>224</v>
       </c>
       <c r="F83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G83" t="n">
         <v>223</v>
@@ -4749,7 +4749,7 @@
         <v>223</v>
       </c>
       <c r="J83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K83" t="n">
         <v>222</v>
@@ -5061,7 +5061,7 @@
         <v>251</v>
       </c>
       <c r="J89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K89" t="n">
         <v>250</v>
@@ -5125,7 +5125,7 @@
         <v>211</v>
       </c>
       <c r="N90" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91">
@@ -5315,7 +5315,7 @@
         <v>842</v>
       </c>
       <c r="H94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-10</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-09-30</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-29</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -1017,7 +1017,7 @@
         <v>91</v>
       </c>
       <c r="N11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -1045,7 +1045,7 @@
         <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
         <v>69</v>
@@ -1522,7 +1522,7 @@
         <v>34</v>
       </c>
       <c r="I21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21" t="n">
         <v>33</v>
@@ -2449,7 +2449,7 @@
         <v>183</v>
       </c>
       <c r="F39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G39" t="n">
         <v>182</v>
@@ -2816,7 +2816,7 @@
         <v>289</v>
       </c>
       <c r="G46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H46" t="n">
         <v>287</v>
@@ -2978,7 +2978,7 @@
         <v>402</v>
       </c>
       <c r="I49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J49" t="n">
         <v>401</v>
@@ -3388,7 +3388,7 @@
         <v>159</v>
       </c>
       <c r="G57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H57" t="n">
         <v>158</v>
@@ -3400,7 +3400,7 @@
         <v>158</v>
       </c>
       <c r="K57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L57" t="n">
         <v>156</v>
@@ -3437,31 +3437,31 @@
         <v>608</v>
       </c>
       <c r="F58" t="n">
+        <v>608</v>
+      </c>
+      <c r="G58" t="n">
         <v>605</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>598</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>592</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>585</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>584</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>582</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>579</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>577</v>
-      </c>
-      <c r="N58" t="n">
-        <v>575</v>
       </c>
     </row>
     <row r="59">
@@ -3489,13 +3489,13 @@
         <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G59" t="n">
         <v>48</v>
       </c>
       <c r="H59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I59" t="n">
         <v>47</v>
@@ -3541,7 +3541,7 @@
         <v>42</v>
       </c>
       <c r="F60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G60" t="n">
         <v>41</v>
@@ -3697,10 +3697,10 @@
         <v>56</v>
       </c>
       <c r="F63" t="n">
+        <v>56</v>
+      </c>
+      <c r="G63" t="n">
         <v>55</v>
-      </c>
-      <c r="G63" t="n">
-        <v>54</v>
       </c>
       <c r="H63" t="n">
         <v>54</v>
@@ -3721,7 +3721,7 @@
         <v>54</v>
       </c>
       <c r="N63" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64">
@@ -4495,7 +4495,7 @@
         <v>291</v>
       </c>
       <c r="L78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M78" t="n">
         <v>290</v>
@@ -4740,7 +4740,7 @@
         <v>224</v>
       </c>
       <c r="G83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H83" t="n">
         <v>223</v>
@@ -4752,7 +4752,7 @@
         <v>223</v>
       </c>
       <c r="K83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L83" t="n">
         <v>222</v>
@@ -5064,7 +5064,7 @@
         <v>251</v>
       </c>
       <c r="K89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L89" t="n">
         <v>250</v>
@@ -5318,7 +5318,7 @@
         <v>842</v>
       </c>
       <c r="I94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-11</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-01</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
         <v>69</v>
@@ -1525,7 +1525,7 @@
         <v>34</v>
       </c>
       <c r="J21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
         <v>33</v>
@@ -2452,7 +2452,7 @@
         <v>183</v>
       </c>
       <c r="G39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H39" t="n">
         <v>182</v>
@@ -2819,7 +2819,7 @@
         <v>289</v>
       </c>
       <c r="H46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I46" t="n">
         <v>287</v>
@@ -2981,7 +2981,7 @@
         <v>402</v>
       </c>
       <c r="J49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K49" t="n">
         <v>401</v>
@@ -3391,7 +3391,7 @@
         <v>159</v>
       </c>
       <c r="H57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" t="n">
         <v>158</v>
@@ -3403,7 +3403,7 @@
         <v>158</v>
       </c>
       <c r="L57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M57" t="n">
         <v>156</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F58" t="n">
         <v>608</v>
       </c>
       <c r="G58" t="n">
+        <v>608</v>
+      </c>
+      <c r="H58" t="n">
         <v>605</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>598</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>592</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>585</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>584</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>582</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>579</v>
-      </c>
-      <c r="N58" t="n">
-        <v>577</v>
       </c>
     </row>
     <row r="59">
@@ -3492,13 +3492,13 @@
         <v>49</v>
       </c>
       <c r="G59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H59" t="n">
         <v>48</v>
       </c>
       <c r="I59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J59" t="n">
         <v>47</v>
@@ -3544,7 +3544,7 @@
         <v>42</v>
       </c>
       <c r="G60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H60" t="n">
         <v>41</v>
@@ -3700,10 +3700,10 @@
         <v>56</v>
       </c>
       <c r="G63" t="n">
+        <v>56</v>
+      </c>
+      <c r="H63" t="n">
         <v>55</v>
-      </c>
-      <c r="H63" t="n">
-        <v>54</v>
       </c>
       <c r="I63" t="n">
         <v>54</v>
@@ -4498,7 +4498,7 @@
         <v>291</v>
       </c>
       <c r="M78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N78" t="n">
         <v>290</v>
@@ -4743,7 +4743,7 @@
         <v>224</v>
       </c>
       <c r="H83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I83" t="n">
         <v>223</v>
@@ -4755,7 +4755,7 @@
         <v>223</v>
       </c>
       <c r="L83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M83" t="n">
         <v>222</v>
@@ -5067,7 +5067,7 @@
         <v>251</v>
       </c>
       <c r="L89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M89" t="n">
         <v>250</v>
@@ -5321,7 +5321,7 @@
         <v>842</v>
       </c>
       <c r="J94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="K94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-12</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-02</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I12" t="n">
         <v>69</v>
@@ -1528,7 +1528,7 @@
         <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L21" t="n">
         <v>33</v>
@@ -2455,7 +2455,7 @@
         <v>183</v>
       </c>
       <c r="H39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I39" t="n">
         <v>182</v>
@@ -2822,7 +2822,7 @@
         <v>289</v>
       </c>
       <c r="I46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J46" t="n">
         <v>287</v>
@@ -2984,7 +2984,7 @@
         <v>402</v>
       </c>
       <c r="K49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L49" t="n">
         <v>401</v>
@@ -3394,7 +3394,7 @@
         <v>159</v>
       </c>
       <c r="I57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J57" t="n">
         <v>158</v>
@@ -3406,7 +3406,7 @@
         <v>158</v>
       </c>
       <c r="M57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N57" t="n">
         <v>156</v>
@@ -3437,31 +3437,31 @@
         <v>611</v>
       </c>
       <c r="F58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="G58" t="n">
         <v>608</v>
       </c>
       <c r="H58" t="n">
+        <v>608</v>
+      </c>
+      <c r="I58" t="n">
         <v>605</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>598</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>592</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>585</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>584</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>582</v>
-      </c>
-      <c r="N58" t="n">
-        <v>579</v>
       </c>
     </row>
     <row r="59">
@@ -3495,13 +3495,13 @@
         <v>49</v>
       </c>
       <c r="H59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I59" t="n">
         <v>48</v>
       </c>
       <c r="J59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" t="n">
         <v>47</v>
@@ -3547,7 +3547,7 @@
         <v>42</v>
       </c>
       <c r="H60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I60" t="n">
         <v>41</v>
@@ -3703,10 +3703,10 @@
         <v>56</v>
       </c>
       <c r="H63" t="n">
+        <v>56</v>
+      </c>
+      <c r="I63" t="n">
         <v>55</v>
-      </c>
-      <c r="I63" t="n">
-        <v>54</v>
       </c>
       <c r="J63" t="n">
         <v>54</v>
@@ -4501,7 +4501,7 @@
         <v>291</v>
       </c>
       <c r="N78" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79">
@@ -4746,7 +4746,7 @@
         <v>224</v>
       </c>
       <c r="I83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J83" t="n">
         <v>223</v>
@@ -4758,7 +4758,7 @@
         <v>223</v>
       </c>
       <c r="M83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N83" t="n">
         <v>222</v>
@@ -5070,7 +5070,7 @@
         <v>251</v>
       </c>
       <c r="M89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N89" t="n">
         <v>250</v>
@@ -5324,7 +5324,7 @@
         <v>842</v>
       </c>
       <c r="K94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-14</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-03</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-02</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
         <v>102</v>
@@ -1054,7 +1054,7 @@
         <v>70</v>
       </c>
       <c r="I12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
         <v>69</v>
@@ -1531,7 +1531,7 @@
         <v>34</v>
       </c>
       <c r="L21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M21" t="n">
         <v>33</v>
@@ -2458,7 +2458,7 @@
         <v>183</v>
       </c>
       <c r="I39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J39" t="n">
         <v>182</v>
@@ -2825,7 +2825,7 @@
         <v>289</v>
       </c>
       <c r="J46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K46" t="n">
         <v>287</v>
@@ -2987,7 +2987,7 @@
         <v>402</v>
       </c>
       <c r="L49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M49" t="n">
         <v>401</v>
@@ -3397,7 +3397,7 @@
         <v>159</v>
       </c>
       <c r="J57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K57" t="n">
         <v>158</v>
@@ -3409,7 +3409,7 @@
         <v>158</v>
       </c>
       <c r="N57" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F58" t="n">
         <v>611</v>
       </c>
       <c r="G58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H58" t="n">
         <v>608</v>
       </c>
       <c r="I58" t="n">
+        <v>608</v>
+      </c>
+      <c r="J58" t="n">
         <v>605</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>598</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>592</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>585</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>584</v>
-      </c>
-      <c r="N58" t="n">
-        <v>582</v>
       </c>
     </row>
     <row r="59">
@@ -3498,13 +3498,13 @@
         <v>49</v>
       </c>
       <c r="I59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J59" t="n">
         <v>48</v>
       </c>
       <c r="K59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L59" t="n">
         <v>47</v>
@@ -3550,7 +3550,7 @@
         <v>42</v>
       </c>
       <c r="I60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J60" t="n">
         <v>41</v>
@@ -3706,10 +3706,10 @@
         <v>56</v>
       </c>
       <c r="I63" t="n">
+        <v>56</v>
+      </c>
+      <c r="J63" t="n">
         <v>55</v>
-      </c>
-      <c r="J63" t="n">
-        <v>54</v>
       </c>
       <c r="K63" t="n">
         <v>54</v>
@@ -4749,7 +4749,7 @@
         <v>224</v>
       </c>
       <c r="J83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K83" t="n">
         <v>223</v>
@@ -4761,7 +4761,7 @@
         <v>223</v>
       </c>
       <c r="N83" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84">
@@ -5073,7 +5073,7 @@
         <v>251</v>
       </c>
       <c r="N89" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90">
@@ -5327,7 +5327,7 @@
         <v>842</v>
       </c>
       <c r="L94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-15</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-04</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-03</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
         <v>102</v>
@@ -1057,7 +1057,7 @@
         <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
         <v>69</v>
@@ -1534,7 +1534,7 @@
         <v>34</v>
       </c>
       <c r="M21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N21" t="n">
         <v>33</v>
@@ -2461,7 +2461,7 @@
         <v>183</v>
       </c>
       <c r="J39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K39" t="n">
         <v>182</v>
@@ -2828,7 +2828,7 @@
         <v>289</v>
       </c>
       <c r="K46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L46" t="n">
         <v>287</v>
@@ -2990,7 +2990,7 @@
         <v>402</v>
       </c>
       <c r="M49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N49" t="n">
         <v>401</v>
@@ -3400,7 +3400,7 @@
         <v>159</v>
       </c>
       <c r="K57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L57" t="n">
         <v>158</v>
@@ -3437,31 +3437,31 @@
         <v>614</v>
       </c>
       <c r="F58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G58" t="n">
         <v>611</v>
       </c>
       <c r="H58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I58" t="n">
         <v>608</v>
       </c>
       <c r="J58" t="n">
+        <v>608</v>
+      </c>
+      <c r="K58" t="n">
         <v>605</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>598</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>592</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>585</v>
-      </c>
-      <c r="N58" t="n">
-        <v>584</v>
       </c>
     </row>
     <row r="59">
@@ -3501,13 +3501,13 @@
         <v>49</v>
       </c>
       <c r="J59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K59" t="n">
         <v>48</v>
       </c>
       <c r="L59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M59" t="n">
         <v>47</v>
@@ -3553,7 +3553,7 @@
         <v>42</v>
       </c>
       <c r="J60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K60" t="n">
         <v>41</v>
@@ -3709,10 +3709,10 @@
         <v>56</v>
       </c>
       <c r="J63" t="n">
+        <v>56</v>
+      </c>
+      <c r="K63" t="n">
         <v>55</v>
-      </c>
-      <c r="K63" t="n">
-        <v>54</v>
       </c>
       <c r="L63" t="n">
         <v>54</v>
@@ -4752,7 +4752,7 @@
         <v>224</v>
       </c>
       <c r="K83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L83" t="n">
         <v>223</v>
@@ -5330,7 +5330,7 @@
         <v>842</v>
       </c>
       <c r="M94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N94" t="n">
         <v>841</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-16</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-06</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-04</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
         <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" t="n">
         <v>102</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
@@ -1060,7 +1060,7 @@
         <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L12" t="n">
         <v>69</v>
@@ -1537,7 +1537,7 @@
         <v>34</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -2464,7 +2464,7 @@
         <v>183</v>
       </c>
       <c r="K39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L39" t="n">
         <v>182</v>
@@ -2831,7 +2831,7 @@
         <v>289</v>
       </c>
       <c r="L46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M46" t="n">
         <v>287</v>
@@ -2993,7 +2993,7 @@
         <v>402</v>
       </c>
       <c r="N49" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50">
@@ -3403,7 +3403,7 @@
         <v>159</v>
       </c>
       <c r="L57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M57" t="n">
         <v>158</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F58" t="n">
         <v>614</v>
       </c>
       <c r="G58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H58" t="n">
         <v>611</v>
       </c>
       <c r="I58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J58" t="n">
         <v>608</v>
       </c>
       <c r="K58" t="n">
+        <v>608</v>
+      </c>
+      <c r="L58" t="n">
         <v>605</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>598</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>592</v>
-      </c>
-      <c r="N58" t="n">
-        <v>585</v>
       </c>
     </row>
     <row r="59">
@@ -3504,13 +3504,13 @@
         <v>49</v>
       </c>
       <c r="K59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L59" t="n">
         <v>48</v>
       </c>
       <c r="M59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N59" t="n">
         <v>47</v>
@@ -3556,7 +3556,7 @@
         <v>42</v>
       </c>
       <c r="K60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L60" t="n">
         <v>41</v>
@@ -3712,10 +3712,10 @@
         <v>56</v>
       </c>
       <c r="K63" t="n">
+        <v>56</v>
+      </c>
+      <c r="L63" t="n">
         <v>55</v>
-      </c>
-      <c r="L63" t="n">
-        <v>54</v>
       </c>
       <c r="M63" t="n">
         <v>54</v>
@@ -4755,7 +4755,7 @@
         <v>224</v>
       </c>
       <c r="L83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M83" t="n">
         <v>223</v>
@@ -5333,7 +5333,7 @@
         <v>842</v>
       </c>
       <c r="N94" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-17</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-07</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-06</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>103</v>
       </c>
       <c r="H2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I2" t="n">
         <v>102</v>
@@ -629,7 +629,7 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>39</v>
@@ -1063,7 +1063,7 @@
         <v>70</v>
       </c>
       <c r="L12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M12" t="n">
         <v>69</v>
@@ -2467,7 +2467,7 @@
         <v>183</v>
       </c>
       <c r="L39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M39" t="n">
         <v>182</v>
@@ -2834,7 +2834,7 @@
         <v>289</v>
       </c>
       <c r="M46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N46" t="n">
         <v>287</v>
@@ -3406,7 +3406,7 @@
         <v>159</v>
       </c>
       <c r="M57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N57" t="n">
         <v>158</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>617</v>
+      </c>
+      <c r="F58" t="n">
         <v>616</v>
-      </c>
-      <c r="F58" t="n">
-        <v>614</v>
       </c>
       <c r="G58" t="n">
         <v>614</v>
       </c>
       <c r="H58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I58" t="n">
         <v>611</v>
       </c>
       <c r="J58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K58" t="n">
         <v>608</v>
       </c>
       <c r="L58" t="n">
+        <v>608</v>
+      </c>
+      <c r="M58" t="n">
         <v>605</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>598</v>
-      </c>
-      <c r="N58" t="n">
-        <v>592</v>
       </c>
     </row>
     <row r="59">
@@ -3507,13 +3507,13 @@
         <v>49</v>
       </c>
       <c r="L59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M59" t="n">
         <v>48</v>
       </c>
       <c r="N59" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
@@ -3559,7 +3559,7 @@
         <v>42</v>
       </c>
       <c r="L60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M60" t="n">
         <v>41</v>
@@ -3715,10 +3715,10 @@
         <v>56</v>
       </c>
       <c r="L63" t="n">
+        <v>56</v>
+      </c>
+      <c r="M63" t="n">
         <v>55</v>
-      </c>
-      <c r="M63" t="n">
-        <v>54</v>
       </c>
       <c r="N63" t="n">
         <v>54</v>
@@ -4758,7 +4758,7 @@
         <v>224</v>
       </c>
       <c r="M83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N83" t="n">
         <v>223</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-18</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-08</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-07</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
         <v>103</v>
       </c>
       <c r="I2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J2" t="n">
         <v>102</v>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
         <v>93</v>
@@ -632,7 +632,7 @@
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
         <v>39</v>
@@ -1066,7 +1066,7 @@
         <v>70</v>
       </c>
       <c r="M12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N12" t="n">
         <v>69</v>
@@ -2470,7 +2470,7 @@
         <v>183</v>
       </c>
       <c r="M39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N39" t="n">
         <v>182</v>
@@ -2837,7 +2837,7 @@
         <v>289</v>
       </c>
       <c r="N46" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F47" t="n">
         <v>144</v>
@@ -3409,7 +3409,7 @@
         <v>159</v>
       </c>
       <c r="N57" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58">
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>619</v>
+      </c>
+      <c r="F58" t="n">
         <v>617</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>616</v>
-      </c>
-      <c r="G58" t="n">
-        <v>614</v>
       </c>
       <c r="H58" t="n">
         <v>614</v>
       </c>
       <c r="I58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="J58" t="n">
         <v>611</v>
       </c>
       <c r="K58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L58" t="n">
         <v>608</v>
       </c>
       <c r="M58" t="n">
+        <v>608</v>
+      </c>
+      <c r="N58" t="n">
         <v>605</v>
-      </c>
-      <c r="N58" t="n">
-        <v>598</v>
       </c>
     </row>
     <row r="59">
@@ -3510,7 +3510,7 @@
         <v>49</v>
       </c>
       <c r="M59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3562,7 +3562,7 @@
         <v>42</v>
       </c>
       <c r="M60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N60" t="n">
         <v>41</v>
@@ -3718,10 +3718,10 @@
         <v>56</v>
       </c>
       <c r="M63" t="n">
+        <v>56</v>
+      </c>
+      <c r="N63" t="n">
         <v>55</v>
-      </c>
-      <c r="N63" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="64">
@@ -4761,7 +4761,7 @@
         <v>224</v>
       </c>
       <c r="N83" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-19</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-09</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-08</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2" t="n">
         <v>103</v>
@@ -537,7 +537,7 @@
         <v>103</v>
       </c>
       <c r="J2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K2" t="n">
         <v>102</v>
@@ -577,7 +577,7 @@
         <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
@@ -635,7 +635,7 @@
         <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
         <v>39</v>
@@ -1069,7 +1069,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F39" t="n">
         <v>183</v>
@@ -2473,7 +2473,7 @@
         <v>183</v>
       </c>
       <c r="N39" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F42" t="n">
         <v>118</v>
@@ -2865,7 +2865,7 @@
         <v>145</v>
       </c>
       <c r="F47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G47" t="n">
         <v>144</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F53" t="n">
         <v>57</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>624</v>
+      </c>
+      <c r="F58" t="n">
         <v>619</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>617</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>616</v>
-      </c>
-      <c r="H58" t="n">
-        <v>614</v>
       </c>
       <c r="I58" t="n">
         <v>614</v>
       </c>
       <c r="J58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K58" t="n">
         <v>611</v>
       </c>
       <c r="L58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M58" t="n">
         <v>608</v>
       </c>
       <c r="N58" t="n">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="59">
@@ -3513,7 +3513,7 @@
         <v>49</v>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60">
@@ -3565,7 +3565,7 @@
         <v>42</v>
       </c>
       <c r="N60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -3721,7 +3721,7 @@
         <v>56</v>
       </c>
       <c r="N63" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
@@ -5309,7 +5309,7 @@
         <v>843</v>
       </c>
       <c r="F94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-20</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-10</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-09</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         <v>105</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
         <v>103</v>
@@ -540,7 +540,7 @@
         <v>103</v>
       </c>
       <c r="K2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L2" t="n">
         <v>102</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
         <v>94</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -638,7 +638,7 @@
         <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
         <v>91</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>70</v>
@@ -2449,7 +2449,7 @@
         <v>184</v>
       </c>
       <c r="F39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G39" t="n">
         <v>183</v>
@@ -2605,7 +2605,7 @@
         <v>119</v>
       </c>
       <c r="F42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G42" t="n">
         <v>118</v>
@@ -2868,7 +2868,7 @@
         <v>145</v>
       </c>
       <c r="G47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H47" t="n">
         <v>144</v>
@@ -3177,7 +3177,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G53" t="n">
         <v>57</v>
@@ -3434,31 +3434,31 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>634</v>
+      </c>
+      <c r="F58" t="n">
         <v>624</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>619</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>617</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>616</v>
-      </c>
-      <c r="I58" t="n">
-        <v>614</v>
       </c>
       <c r="J58" t="n">
         <v>614</v>
       </c>
       <c r="K58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L58" t="n">
         <v>611</v>
       </c>
       <c r="M58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N58" t="n">
         <v>608</v>
@@ -5312,7 +5312,7 @@
         <v>843</v>
       </c>
       <c r="G94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-21</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-11</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-10</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
         <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H2" t="n">
         <v>103</v>
@@ -543,7 +543,7 @@
         <v>103</v>
       </c>
       <c r="L2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M2" t="n">
         <v>102</v>
@@ -577,13 +577,13 @@
         <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
         <v>94</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I3" t="n">
         <v>93</v>
@@ -641,7 +641,7 @@
         <v>40</v>
       </c>
       <c r="J4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
         <v>39</v>
@@ -993,7 +993,7 @@
         <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
         <v>91</v>
@@ -1045,7 +1045,7 @@
         <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
         <v>37</v>
@@ -2452,7 +2452,7 @@
         <v>184</v>
       </c>
       <c r="G39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H39" t="n">
         <v>183</v>
@@ -2608,7 +2608,7 @@
         <v>119</v>
       </c>
       <c r="G42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H42" t="n">
         <v>118</v>
@@ -2871,7 +2871,7 @@
         <v>145</v>
       </c>
       <c r="H47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I47" t="n">
         <v>144</v>
@@ -3180,7 +3180,7 @@
         <v>58</v>
       </c>
       <c r="G53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H53" t="n">
         <v>57</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>636</v>
+      </c>
+      <c r="F58" t="n">
         <v>634</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>624</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>619</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>617</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>616</v>
-      </c>
-      <c r="J58" t="n">
-        <v>614</v>
       </c>
       <c r="K58" t="n">
         <v>614</v>
       </c>
       <c r="L58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M58" t="n">
         <v>611</v>
       </c>
       <c r="N58" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="59">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F90" t="n">
         <v>211</v>
@@ -5315,7 +5315,7 @@
         <v>843</v>
       </c>
       <c r="H94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-22</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-12</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-11</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>105</v>
       </c>
       <c r="H2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I2" t="n">
         <v>103</v>
@@ -546,7 +546,7 @@
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N2" t="n">
         <v>102</v>
@@ -580,13 +580,13 @@
         <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
         <v>94</v>
       </c>
       <c r="I3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" t="n">
         <v>93</v>
@@ -644,7 +644,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
         <v>39</v>
@@ -996,7 +996,7 @@
         <v>93</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H11" t="n">
         <v>91</v>
@@ -1048,7 +1048,7 @@
         <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" t="n">
         <v>70</v>
@@ -1253,7 +1253,7 @@
         <v>38</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
         <v>37</v>
@@ -2455,7 +2455,7 @@
         <v>184</v>
       </c>
       <c r="H39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I39" t="n">
         <v>183</v>
@@ -2611,7 +2611,7 @@
         <v>119</v>
       </c>
       <c r="H42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I42" t="n">
         <v>118</v>
@@ -2874,7 +2874,7 @@
         <v>145</v>
       </c>
       <c r="I47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J47" t="n">
         <v>144</v>
@@ -3183,7 +3183,7 @@
         <v>58</v>
       </c>
       <c r="H53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I53" t="n">
         <v>57</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F57" t="n">
         <v>159</v>
@@ -3434,31 +3434,31 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>638</v>
+      </c>
+      <c r="F58" t="n">
         <v>636</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>634</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>624</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>619</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>617</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>616</v>
-      </c>
-      <c r="K58" t="n">
-        <v>614</v>
       </c>
       <c r="L58" t="n">
         <v>614</v>
       </c>
       <c r="M58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="N58" t="n">
         <v>611</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F78" t="n">
         <v>291</v>
@@ -5101,7 +5101,7 @@
         <v>217</v>
       </c>
       <c r="F90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G90" t="n">
         <v>211</v>
@@ -5318,7 +5318,7 @@
         <v>843</v>
       </c>
       <c r="I94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-24</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-14</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-12</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
         <v>105</v>
       </c>
       <c r="I2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J2" t="n">
         <v>103</v>
@@ -549,7 +549,7 @@
         <v>103</v>
       </c>
       <c r="N2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -583,13 +583,13 @@
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
         <v>94</v>
       </c>
       <c r="J3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="n">
         <v>93</v>
@@ -647,7 +647,7 @@
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>39</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
         <v>93</v>
@@ -999,7 +999,7 @@
         <v>93</v>
       </c>
       <c r="H11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I11" t="n">
         <v>91</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>71</v>
@@ -1051,7 +1051,7 @@
         <v>71</v>
       </c>
       <c r="H12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" t="n">
         <v>70</v>
@@ -1256,7 +1256,7 @@
         <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16" t="n">
         <v>37</v>
@@ -2458,7 +2458,7 @@
         <v>184</v>
       </c>
       <c r="I39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J39" t="n">
         <v>183</v>
@@ -2614,7 +2614,7 @@
         <v>119</v>
       </c>
       <c r="I42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J42" t="n">
         <v>118</v>
@@ -2877,7 +2877,7 @@
         <v>145</v>
       </c>
       <c r="J47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K47" t="n">
         <v>144</v>
@@ -3186,7 +3186,7 @@
         <v>58</v>
       </c>
       <c r="I53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J53" t="n">
         <v>57</v>
@@ -3385,7 +3385,7 @@
         <v>160</v>
       </c>
       <c r="F57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>642</v>
+      </c>
+      <c r="F58" t="n">
         <v>638</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>636</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>634</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>624</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>619</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>617</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>616</v>
-      </c>
-      <c r="L58" t="n">
-        <v>614</v>
       </c>
       <c r="M58" t="n">
         <v>614</v>
       </c>
       <c r="N58" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="59">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="E78" t="n">
+        <v>294</v>
+      </c>
+      <c r="F78" t="n">
         <v>293</v>
-      </c>
-      <c r="F78" t="n">
-        <v>291</v>
       </c>
       <c r="G78" t="n">
         <v>291</v>
@@ -5104,7 +5104,7 @@
         <v>217</v>
       </c>
       <c r="G90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H90" t="n">
         <v>211</v>
@@ -5321,7 +5321,7 @@
         <v>843</v>
       </c>
       <c r="J94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-25</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-15</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-14</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         <v>105</v>
       </c>
       <c r="J2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -586,13 +586,13 @@
         <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" t="n">
         <v>94</v>
       </c>
       <c r="K3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L3" t="n">
         <v>93</v>
@@ -650,7 +650,7 @@
         <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
         <v>39</v>
@@ -993,7 +993,7 @@
         <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" t="n">
         <v>93</v>
@@ -1002,7 +1002,7 @@
         <v>93</v>
       </c>
       <c r="I11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J11" t="n">
         <v>91</v>
@@ -1045,7 +1045,7 @@
         <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G12" t="n">
         <v>71</v>
@@ -1054,7 +1054,7 @@
         <v>71</v>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J12" t="n">
         <v>70</v>
@@ -1259,7 +1259,7 @@
         <v>38</v>
       </c>
       <c r="H16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16" t="n">
         <v>37</v>
@@ -2461,7 +2461,7 @@
         <v>184</v>
       </c>
       <c r="J39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K39" t="n">
         <v>183</v>
@@ -2617,7 +2617,7 @@
         <v>119</v>
       </c>
       <c r="J42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K42" t="n">
         <v>118</v>
@@ -2880,7 +2880,7 @@
         <v>145</v>
       </c>
       <c r="K47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L47" t="n">
         <v>144</v>
@@ -3189,7 +3189,7 @@
         <v>58</v>
       </c>
       <c r="J53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K53" t="n">
         <v>57</v>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F57" t="n">
         <v>160</v>
       </c>
       <c r="G57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H57" t="n">
         <v>159</v>
@@ -3434,31 +3434,31 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>643</v>
+      </c>
+      <c r="F58" t="n">
         <v>642</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>638</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>636</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>634</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>624</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>619</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>617</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>616</v>
-      </c>
-      <c r="M58" t="n">
-        <v>614</v>
       </c>
       <c r="N58" t="n">
         <v>614</v>
@@ -4477,10 +4477,10 @@
         <v>294</v>
       </c>
       <c r="F78" t="n">
+        <v>294</v>
+      </c>
+      <c r="G78" t="n">
         <v>293</v>
-      </c>
-      <c r="G78" t="n">
-        <v>291</v>
       </c>
       <c r="H78" t="n">
         <v>291</v>
@@ -5107,7 +5107,7 @@
         <v>217</v>
       </c>
       <c r="H90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I90" t="n">
         <v>211</v>
@@ -5324,7 +5324,7 @@
         <v>843</v>
       </c>
       <c r="K94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="L94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-26</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-25</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-16</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-15</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         <v>105</v>
       </c>
       <c r="K2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
         <v>103</v>
@@ -589,13 +589,13 @@
         <v>95</v>
       </c>
       <c r="J3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" t="n">
         <v>94</v>
       </c>
       <c r="L3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
         <v>93</v>
@@ -653,7 +653,7 @@
         <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -996,7 +996,7 @@
         <v>94</v>
       </c>
       <c r="G11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" t="n">
         <v>93</v>
@@ -1005,7 +1005,7 @@
         <v>93</v>
       </c>
       <c r="J11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" t="n">
         <v>91</v>
@@ -1048,7 +1048,7 @@
         <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" t="n">
         <v>71</v>
@@ -1057,7 +1057,7 @@
         <v>71</v>
       </c>
       <c r="J12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
         <v>70</v>
@@ -1262,7 +1262,7 @@
         <v>38</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
         <v>37</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F27" t="n">
         <v>216</v>
@@ -2464,7 +2464,7 @@
         <v>184</v>
       </c>
       <c r="K39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L39" t="n">
         <v>183</v>
@@ -2620,7 +2620,7 @@
         <v>119</v>
       </c>
       <c r="K42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L42" t="n">
         <v>118</v>
@@ -2883,7 +2883,7 @@
         <v>145</v>
       </c>
       <c r="L47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M47" t="n">
         <v>144</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F52" t="n">
         <v>98</v>
@@ -3192,7 +3192,7 @@
         <v>58</v>
       </c>
       <c r="K53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L53" t="n">
         <v>57</v>
@@ -3385,13 +3385,13 @@
         <v>161</v>
       </c>
       <c r="F57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G57" t="n">
         <v>160</v>
       </c>
       <c r="H57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>644</v>
+      </c>
+      <c r="F58" t="n">
         <v>643</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>642</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>638</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>636</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>634</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>624</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>619</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>617</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>616</v>
-      </c>
-      <c r="N58" t="n">
-        <v>614</v>
       </c>
     </row>
     <row r="59">
@@ -4480,10 +4480,10 @@
         <v>294</v>
       </c>
       <c r="G78" t="n">
+        <v>294</v>
+      </c>
+      <c r="H78" t="n">
         <v>293</v>
-      </c>
-      <c r="H78" t="n">
-        <v>291</v>
       </c>
       <c r="I78" t="n">
         <v>291</v>
@@ -5110,7 +5110,7 @@
         <v>217</v>
       </c>
       <c r="I90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J90" t="n">
         <v>211</v>
@@ -5327,7 +5327,7 @@
         <v>843</v>
       </c>
       <c r="L94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-27</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-26</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-17</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-16</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
         <v>105</v>
       </c>
       <c r="L2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M2" t="n">
         <v>103</v>
@@ -592,13 +592,13 @@
         <v>95</v>
       </c>
       <c r="K3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="n">
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="n">
         <v>93</v>
@@ -999,7 +999,7 @@
         <v>94</v>
       </c>
       <c r="H11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="n">
         <v>93</v>
@@ -1008,7 +1008,7 @@
         <v>93</v>
       </c>
       <c r="K11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L11" t="n">
         <v>91</v>
@@ -1051,7 +1051,7 @@
         <v>72</v>
       </c>
       <c r="H12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" t="n">
         <v>71</v>
@@ -1060,7 +1060,7 @@
         <v>71</v>
       </c>
       <c r="K12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L12" t="n">
         <v>70</v>
@@ -1265,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
         <v>37</v>
@@ -1825,7 +1825,7 @@
         <v>217</v>
       </c>
       <c r="F27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G27" t="n">
         <v>216</v>
@@ -2467,7 +2467,7 @@
         <v>184</v>
       </c>
       <c r="L39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M39" t="n">
         <v>183</v>
@@ -2623,7 +2623,7 @@
         <v>119</v>
       </c>
       <c r="L42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M42" t="n">
         <v>118</v>
@@ -2886,7 +2886,7 @@
         <v>145</v>
       </c>
       <c r="M47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N47" t="n">
         <v>144</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F49" t="n">
         <v>402</v>
@@ -3125,7 +3125,7 @@
         <v>99</v>
       </c>
       <c r="F52" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G52" t="n">
         <v>98</v>
@@ -3195,7 +3195,7 @@
         <v>58</v>
       </c>
       <c r="L53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M53" t="n">
         <v>57</v>
@@ -3388,13 +3388,13 @@
         <v>161</v>
       </c>
       <c r="G57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" t="n">
         <v>160</v>
       </c>
       <c r="I57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>647</v>
+      </c>
+      <c r="F58" t="n">
         <v>644</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>643</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>642</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>638</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>636</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>634</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>624</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>619</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>617</v>
-      </c>
-      <c r="N58" t="n">
-        <v>616</v>
       </c>
     </row>
     <row r="59">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F66" t="n">
         <v>76</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F68" t="n">
         <v>88</v>
@@ -4483,10 +4483,10 @@
         <v>294</v>
       </c>
       <c r="H78" t="n">
+        <v>294</v>
+      </c>
+      <c r="I78" t="n">
         <v>293</v>
-      </c>
-      <c r="I78" t="n">
-        <v>291</v>
       </c>
       <c r="J78" t="n">
         <v>291</v>
@@ -5113,7 +5113,7 @@
         <v>217</v>
       </c>
       <c r="J90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K90" t="n">
         <v>211</v>
@@ -5330,7 +5330,7 @@
         <v>843</v>
       </c>
       <c r="M94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N94" t="n">
         <v>842</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-28</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-27</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-26</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-18</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-17</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         <v>105</v>
       </c>
       <c r="M2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N2" t="n">
         <v>103</v>
@@ -595,13 +595,13 @@
         <v>95</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M3" t="n">
         <v>94</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
         <v>94</v>
@@ -1002,7 +1002,7 @@
         <v>94</v>
       </c>
       <c r="I11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" t="n">
         <v>93</v>
@@ -1011,7 +1011,7 @@
         <v>93</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M11" t="n">
         <v>91</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
         <v>72</v>
@@ -1054,7 +1054,7 @@
         <v>72</v>
       </c>
       <c r="I12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12" t="n">
         <v>71</v>
@@ -1063,7 +1063,7 @@
         <v>71</v>
       </c>
       <c r="L12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
         <v>70</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
         <v>38</v>
@@ -1268,7 +1268,7 @@
         <v>38</v>
       </c>
       <c r="K16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
         <v>37</v>
@@ -1828,7 +1828,7 @@
         <v>217</v>
       </c>
       <c r="G27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H27" t="n">
         <v>216</v>
@@ -2470,7 +2470,7 @@
         <v>184</v>
       </c>
       <c r="M39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N39" t="n">
         <v>183</v>
@@ -2626,7 +2626,7 @@
         <v>119</v>
       </c>
       <c r="M42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N42" t="n">
         <v>118</v>
@@ -2889,7 +2889,7 @@
         <v>145</v>
       </c>
       <c r="N47" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48">
@@ -2969,7 +2969,7 @@
         <v>403</v>
       </c>
       <c r="F49" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G49" t="n">
         <v>402</v>
@@ -3128,7 +3128,7 @@
         <v>99</v>
       </c>
       <c r="G52" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H52" t="n">
         <v>98</v>
@@ -3198,7 +3198,7 @@
         <v>58</v>
       </c>
       <c r="M53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N53" t="n">
         <v>57</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F57" t="n">
         <v>161</v>
@@ -3391,13 +3391,13 @@
         <v>161</v>
       </c>
       <c r="H57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I57" t="n">
         <v>160</v>
       </c>
       <c r="J57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>649</v>
+      </c>
+      <c r="F58" t="n">
         <v>647</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>644</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>643</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>642</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>638</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>636</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>634</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>624</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>619</v>
-      </c>
-      <c r="N58" t="n">
-        <v>617</v>
       </c>
     </row>
     <row r="59">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F63" t="n">
         <v>56</v>
@@ -3853,7 +3853,7 @@
         <v>77</v>
       </c>
       <c r="F66" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G66" t="n">
         <v>76</v>
@@ -3957,7 +3957,7 @@
         <v>89</v>
       </c>
       <c r="F68" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G68" t="n">
         <v>88</v>
@@ -4486,10 +4486,10 @@
         <v>294</v>
       </c>
       <c r="I78" t="n">
+        <v>294</v>
+      </c>
+      <c r="J78" t="n">
         <v>293</v>
-      </c>
-      <c r="J78" t="n">
-        <v>291</v>
       </c>
       <c r="K78" t="n">
         <v>291</v>
@@ -5116,7 +5116,7 @@
         <v>217</v>
       </c>
       <c r="K90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L90" t="n">
         <v>211</v>
@@ -5333,7 +5333,7 @@
         <v>843</v>
       </c>
       <c r="N94" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-29</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-28</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-27</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-26</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-25</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-19</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-18</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>105</v>
       </c>
       <c r="N2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -598,7 +598,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="n">
         <v>94</v>
@@ -993,7 +993,7 @@
         <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" t="n">
         <v>94</v>
@@ -1005,7 +1005,7 @@
         <v>94</v>
       </c>
       <c r="J11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="n">
         <v>93</v>
@@ -1014,7 +1014,7 @@
         <v>93</v>
       </c>
       <c r="M11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N11" t="n">
         <v>91</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="E12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F12" t="n">
         <v>73</v>
-      </c>
-      <c r="F12" t="n">
-        <v>72</v>
       </c>
       <c r="G12" t="n">
         <v>72</v>
@@ -1057,7 +1057,7 @@
         <v>72</v>
       </c>
       <c r="J12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
         <v>71</v>
@@ -1066,7 +1066,7 @@
         <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
         <v>38</v>
@@ -1271,7 +1271,7 @@
         <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
         <v>37</v>
@@ -1831,7 +1831,7 @@
         <v>217</v>
       </c>
       <c r="H27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I27" t="n">
         <v>216</v>
@@ -2473,7 +2473,7 @@
         <v>184</v>
       </c>
       <c r="N39" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2629,7 @@
         <v>119</v>
       </c>
       <c r="N42" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43">
@@ -2972,7 +2972,7 @@
         <v>403</v>
       </c>
       <c r="G49" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H49" t="n">
         <v>402</v>
@@ -3131,7 +3131,7 @@
         <v>99</v>
       </c>
       <c r="H52" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I52" t="n">
         <v>98</v>
@@ -3201,7 +3201,7 @@
         <v>58</v>
       </c>
       <c r="N53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -3385,7 +3385,7 @@
         <v>162</v>
       </c>
       <c r="F57" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G57" t="n">
         <v>161</v>
@@ -3394,13 +3394,13 @@
         <v>161</v>
       </c>
       <c r="I57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J57" t="n">
         <v>160</v>
       </c>
       <c r="K57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>651</v>
+      </c>
+      <c r="F58" t="n">
         <v>649</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>647</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>644</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>643</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>642</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>638</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>636</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>634</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>624</v>
-      </c>
-      <c r="N58" t="n">
-        <v>619</v>
       </c>
     </row>
     <row r="59">
@@ -3697,7 +3697,7 @@
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G63" t="n">
         <v>56</v>
@@ -3856,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="G66" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H66" t="n">
         <v>76</v>
@@ -3960,7 +3960,7 @@
         <v>89</v>
       </c>
       <c r="G68" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H68" t="n">
         <v>88</v>
@@ -4489,10 +4489,10 @@
         <v>294</v>
       </c>
       <c r="J78" t="n">
+        <v>294</v>
+      </c>
+      <c r="K78" t="n">
         <v>293</v>
-      </c>
-      <c r="K78" t="n">
-        <v>291</v>
       </c>
       <c r="L78" t="n">
         <v>291</v>
@@ -5119,7 +5119,7 @@
         <v>217</v>
       </c>
       <c r="L90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M90" t="n">
         <v>211</v>

--- a/history_stoicether.xlsx
+++ b/history_stoicether.xlsx
@@ -451,52 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Views_2026-10-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Views_2026-10-29</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-28</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-27</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-25</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-24</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-22</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-21</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Views_2026-10-20</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Views_2026-10-19</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         <v>95</v>
       </c>
       <c r="N3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -996,7 +996,7 @@
         <v>95</v>
       </c>
       <c r="G11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
         <v>94</v>
@@ -1008,7 +1008,7 @@
         <v>94</v>
       </c>
       <c r="K11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L11" t="n">
         <v>93</v>
@@ -1017,7 +1017,7 @@
         <v>93</v>
       </c>
       <c r="N11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -1045,10 +1045,10 @@
         <v>74</v>
       </c>
       <c r="F12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G12" t="n">
         <v>73</v>
-      </c>
-      <c r="G12" t="n">
-        <v>72</v>
       </c>
       <c r="H12" t="n">
         <v>72</v>
@@ -1060,7 +1060,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L12" t="n">
         <v>71</v>
@@ -1069,7 +1069,7 @@
         <v>71</v>
       </c>
       <c r="N12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -1100,7 +1100,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" t="n">
         <v>38</v>
@@ -1274,7 +1274,7 @@
         <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N16" t="n">
         <v>37</v>
@@ -1834,7 +1834,7 @@
         <v>217</v>
       </c>
       <c r="I27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J27" t="n">
         <v>216</v>
@@ -2975,7 +2975,7 @@
         <v>403</v>
       </c>
       <c r="H49" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I49" t="n">
         <v>402</v>
@@ -3134,7 +3134,7 @@
         <v>99</v>
       </c>
       <c r="I52" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J52" t="n">
         <v>98</v>
@@ -3388,7 +3388,7 @@
         <v>162</v>
       </c>
       <c r="G57" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H57" t="n">
         <v>161</v>
@@ -3397,13 +3397,13 @@
         <v>161</v>
       </c>
       <c r="J57" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K57" t="n">
         <v>160</v>
       </c>
       <c r="L57" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M57" t="n">
         <v>159</v>
@@ -3434,34 +3434,34 @@
         </is>
       </c>
       <c r="E58" t="n">
+        <v>658</v>
+      </c>
+      <c r="F58" t="n">
         <v>651</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>649</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>647</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>644</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>643</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>642</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>638</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>636</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>634</v>
-      </c>
-      <c r="N58" t="n">
-        <v>624</v>
       </c>
     </row>
     <row r="59">
@@ -3700,7 +3700,7 @@
         <v>58</v>
       </c>
       <c r="G63" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H63" t="n">
         <v>56</v>
@@ -3859,7 +3859,7 @@
         <v>77</v>
       </c>
       <c r="H66" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I66" t="n">
         <v>76</v>
@@ -3963,7 +3963,7 @@
         <v>89</v>
       </c>
       <c r="H68" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I68" t="n">
         <v>88</v>
@@ -4492,10 +4492,10 @@
         <v>294</v>
       </c>
       <c r="K78" t="n">
+        <v>294</v>
+      </c>
+      <c r="L78" t="n">
         <v>293</v>
-      </c>
-      <c r="L78" t="n">
-        <v>291</v>
       </c>
       <c r="M78" t="n">
         <v>291</v>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F86" t="n">
         <v>53</v>
@@ -5122,7 +5122,7 @@
         <v>217</v>
       </c>
       <c r="M90" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N90" t="n">
         <v>211</v>
